--- a/statistics_files/2026/2026_99_d_circulation_unique_daily_borrowers.xlsx
+++ b/statistics_files/2026/2026_99_d_circulation_unique_daily_borrowers.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\George\Documents\github\next_statistics\statistics_files\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E62EBE14-901A-419F-BD0A-85C04920BB48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE37857D-B281-479A-B459-3B3949ACC645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="822" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="January" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,18 @@
     <sheet name="December" sheetId="12" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">April!$A$3:$AG$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">April!$A$3:$AG$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">August!$A$3:$AG$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">December!$A$3:$AG$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">February!$A$3:$AG$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">January!$A$3:$AG$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">July!$A$3:$AG$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">June!$A$3:$AG$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">March!$A$3:$AG$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">May!$A$3:$AG$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">November!$A$3:$AG$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">October!$A$3:$AG$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">September!$A$3:$AG$3</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -40,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="74">
   <si>
     <t>branchname</t>
   </si>
@@ -259,6 +269,9 @@
   </si>
   <si>
     <t>2026-07-01 - 2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-08-01 - 2026-08-30</t>
   </si>
 </sst>
 </file>
@@ -5701,6 +5714,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:AG3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6988,6 +7002,7 @@
       <c r="AG56" s="1"/>
     </row>
   </sheetData>
+  <autoFilter ref="A3:AG3" xr:uid="{00000000-0001-0000-0900-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8275,6 +8290,7 @@
       <c r="AG56" s="1"/>
     </row>
   </sheetData>
+  <autoFilter ref="A3:AG3" xr:uid="{00000000-0001-0000-0A00-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -9562,6 +9578,7 @@
       <c r="AG56" s="1"/>
     </row>
   </sheetData>
+  <autoFilter ref="A3:AG3" xr:uid="{00000000-0001-0000-0B00-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -13990,6 +14007,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:AG3" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -18705,6 +18723,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:AG3" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -23414,6 +23433,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:AG3" xr:uid="{00000000-0001-0000-0300-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -27895,6 +27915,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:AG3" xr:uid="{00000000-0001-0000-0400-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -32395,6 +32416,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:AG3" xr:uid="{00000000-0001-0000-0500-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -36936,6 +36958,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:AG3" xr:uid="{00000000-0001-0000-0600-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -36943,6 +36966,4661 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet8"/>
+  <dimension ref="A1:AG56"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="50.7109375" customWidth="1"/>
+    <col min="2" max="32" width="12.7109375" customWidth="1"/>
+    <col min="33" max="33" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:33" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2">
+        <v>16</v>
+      </c>
+      <c r="R1" s="2">
+        <v>17</v>
+      </c>
+      <c r="S1" s="2">
+        <v>18</v>
+      </c>
+      <c r="T1" s="2">
+        <v>19</v>
+      </c>
+      <c r="U1" s="2">
+        <v>20</v>
+      </c>
+      <c r="V1" s="2">
+        <v>21</v>
+      </c>
+      <c r="W1" s="2">
+        <v>22</v>
+      </c>
+      <c r="X1" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="2">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="2">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="2">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="2">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="2">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="2">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="2">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="2">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C2" s="3">
+        <v>46236</v>
+      </c>
+      <c r="D2" s="3">
+        <v>46237</v>
+      </c>
+      <c r="E2" s="3">
+        <v>46238</v>
+      </c>
+      <c r="F2" s="3">
+        <v>46239</v>
+      </c>
+      <c r="G2" s="3">
+        <v>46240</v>
+      </c>
+      <c r="H2" s="3">
+        <v>46241</v>
+      </c>
+      <c r="I2" s="3">
+        <v>46242</v>
+      </c>
+      <c r="J2" s="3">
+        <v>46243</v>
+      </c>
+      <c r="K2" s="3">
+        <v>46244</v>
+      </c>
+      <c r="L2" s="3">
+        <v>46245</v>
+      </c>
+      <c r="M2" s="3">
+        <v>46246</v>
+      </c>
+      <c r="N2" s="3">
+        <v>46247</v>
+      </c>
+      <c r="O2" s="3">
+        <v>46248</v>
+      </c>
+      <c r="P2" s="3">
+        <v>46249</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>46250</v>
+      </c>
+      <c r="R2" s="3">
+        <v>46251</v>
+      </c>
+      <c r="S2" s="3">
+        <v>46252</v>
+      </c>
+      <c r="T2" s="3">
+        <v>46253</v>
+      </c>
+      <c r="U2" s="3">
+        <v>46254</v>
+      </c>
+      <c r="V2" s="3">
+        <v>46255</v>
+      </c>
+      <c r="W2" s="3">
+        <v>46256</v>
+      </c>
+      <c r="X2" s="3">
+        <v>46257</v>
+      </c>
+      <c r="Y2" s="3">
+        <v>46258</v>
+      </c>
+      <c r="Z2" s="3">
+        <v>46259</v>
+      </c>
+      <c r="AA2" s="3">
+        <v>46260</v>
+      </c>
+      <c r="AB2" s="3">
+        <v>46261</v>
+      </c>
+      <c r="AC2" s="3">
+        <v>46262</v>
+      </c>
+      <c r="AD2" s="3">
+        <v>46263</v>
+      </c>
+      <c r="AE2" s="3">
+        <v>46264</v>
+      </c>
+      <c r="AF2" s="3">
+        <v>46265</v>
+      </c>
+      <c r="AG2" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O3" t="s">
+        <v>6</v>
+      </c>
+      <c r="P3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R3" t="s">
+        <v>9</v>
+      </c>
+      <c r="S3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T3" t="s">
+        <v>11</v>
+      </c>
+      <c r="U3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V3" t="s">
+        <v>6</v>
+      </c>
+      <c r="W3" t="s">
+        <v>7</v>
+      </c>
+      <c r="X3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="1">
+        <v>24</v>
+      </c>
+      <c r="C4" s="1">
+        <v>6</v>
+      </c>
+      <c r="D4" s="1">
+        <v>83</v>
+      </c>
+      <c r="E4" s="1">
+        <v>53</v>
+      </c>
+      <c r="F4" s="1">
+        <v>65</v>
+      </c>
+      <c r="G4" s="1">
+        <v>84</v>
+      </c>
+      <c r="H4" s="1">
+        <v>42</v>
+      </c>
+      <c r="I4" s="1">
+        <v>32</v>
+      </c>
+      <c r="J4" s="1">
+        <v>6</v>
+      </c>
+      <c r="K4" s="1">
+        <v>67</v>
+      </c>
+      <c r="L4" s="1">
+        <v>60</v>
+      </c>
+      <c r="M4" s="1">
+        <v>54</v>
+      </c>
+      <c r="N4" s="1">
+        <v>65</v>
+      </c>
+      <c r="O4" s="1">
+        <v>47</v>
+      </c>
+      <c r="P4" s="1">
+        <v>45</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>4</v>
+      </c>
+      <c r="R4" s="1">
+        <v>69</v>
+      </c>
+      <c r="S4" s="1">
+        <v>41</v>
+      </c>
+      <c r="T4" s="1">
+        <v>67</v>
+      </c>
+      <c r="U4" s="1">
+        <v>51</v>
+      </c>
+      <c r="V4" s="1">
+        <v>54</v>
+      </c>
+      <c r="W4" s="1">
+        <v>27</v>
+      </c>
+      <c r="X4" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="1">
+        <v>81</v>
+      </c>
+      <c r="Z4" s="1">
+        <v>55</v>
+      </c>
+      <c r="AA4" s="1">
+        <v>65</v>
+      </c>
+      <c r="AB4" s="1">
+        <v>69</v>
+      </c>
+      <c r="AC4" s="1">
+        <v>56</v>
+      </c>
+      <c r="AD4" s="1">
+        <v>36</v>
+      </c>
+      <c r="AE4" s="1">
+        <v>4</v>
+      </c>
+      <c r="AF4" s="1">
+        <v>4</v>
+      </c>
+      <c r="AG4" s="1">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5">
+        <v>17</v>
+      </c>
+      <c r="D5">
+        <v>45</v>
+      </c>
+      <c r="E5">
+        <v>37</v>
+      </c>
+      <c r="F5">
+        <v>55</v>
+      </c>
+      <c r="G5">
+        <v>44</v>
+      </c>
+      <c r="H5">
+        <v>25</v>
+      </c>
+      <c r="I5">
+        <v>21</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>47</v>
+      </c>
+      <c r="L5">
+        <v>49</v>
+      </c>
+      <c r="M5">
+        <v>39</v>
+      </c>
+      <c r="N5">
+        <v>26</v>
+      </c>
+      <c r="O5">
+        <v>31</v>
+      </c>
+      <c r="P5">
+        <v>23</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>47</v>
+      </c>
+      <c r="S5">
+        <v>38</v>
+      </c>
+      <c r="T5">
+        <v>45</v>
+      </c>
+      <c r="U5">
+        <v>49</v>
+      </c>
+      <c r="V5">
+        <v>34</v>
+      </c>
+      <c r="W5">
+        <v>20</v>
+      </c>
+      <c r="X5">
+        <v>2</v>
+      </c>
+      <c r="Y5">
+        <v>49</v>
+      </c>
+      <c r="Z5">
+        <v>37</v>
+      </c>
+      <c r="AA5">
+        <v>41</v>
+      </c>
+      <c r="AB5">
+        <v>36</v>
+      </c>
+      <c r="AC5">
+        <v>79</v>
+      </c>
+      <c r="AD5">
+        <v>19</v>
+      </c>
+      <c r="AE5">
+        <v>1</v>
+      </c>
+      <c r="AF5">
+        <v>43</v>
+      </c>
+      <c r="AG5">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1">
+        <v>63</v>
+      </c>
+      <c r="C6" s="1">
+        <v>44</v>
+      </c>
+      <c r="D6" s="1">
+        <v>76</v>
+      </c>
+      <c r="E6" s="1">
+        <v>94</v>
+      </c>
+      <c r="F6" s="1">
+        <v>82</v>
+      </c>
+      <c r="G6" s="1">
+        <v>97</v>
+      </c>
+      <c r="H6" s="1">
+        <v>74</v>
+      </c>
+      <c r="I6" s="1">
+        <v>59</v>
+      </c>
+      <c r="J6" s="1">
+        <v>44</v>
+      </c>
+      <c r="K6" s="1">
+        <v>72</v>
+      </c>
+      <c r="L6" s="1">
+        <v>75</v>
+      </c>
+      <c r="M6" s="1">
+        <v>82</v>
+      </c>
+      <c r="N6" s="1">
+        <v>69</v>
+      </c>
+      <c r="O6" s="1">
+        <v>45</v>
+      </c>
+      <c r="P6" s="1">
+        <v>59</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>54</v>
+      </c>
+      <c r="R6" s="1">
+        <v>21</v>
+      </c>
+      <c r="S6" s="1">
+        <v>44</v>
+      </c>
+      <c r="T6" s="1">
+        <v>82</v>
+      </c>
+      <c r="U6" s="1">
+        <v>75</v>
+      </c>
+      <c r="V6" s="1">
+        <v>8</v>
+      </c>
+      <c r="W6" s="1">
+        <v>72</v>
+      </c>
+      <c r="X6" s="1">
+        <v>58</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>67</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>88</v>
+      </c>
+      <c r="AA6" s="1">
+        <v>68</v>
+      </c>
+      <c r="AB6" s="1">
+        <v>72</v>
+      </c>
+      <c r="AC6" s="1">
+        <v>68</v>
+      </c>
+      <c r="AD6" s="1">
+        <v>60</v>
+      </c>
+      <c r="AE6" s="1">
+        <v>43</v>
+      </c>
+      <c r="AF6" s="1">
+        <v>69</v>
+      </c>
+      <c r="AG6" s="1">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>4</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>2</v>
+      </c>
+      <c r="N7">
+        <v>2</v>
+      </c>
+      <c r="P7">
+        <v>2</v>
+      </c>
+      <c r="R7">
+        <v>4</v>
+      </c>
+      <c r="T7">
+        <v>5</v>
+      </c>
+      <c r="U7">
+        <v>3</v>
+      </c>
+      <c r="W7">
+        <v>3</v>
+      </c>
+      <c r="Y7">
+        <v>4</v>
+      </c>
+      <c r="AA7">
+        <v>4</v>
+      </c>
+      <c r="AB7">
+        <v>1</v>
+      </c>
+      <c r="AC7">
+        <v>2</v>
+      </c>
+      <c r="AF7">
+        <v>4</v>
+      </c>
+      <c r="AG7">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="1">
+        <v>38</v>
+      </c>
+      <c r="C8" s="1">
+        <v>31</v>
+      </c>
+      <c r="D8" s="1">
+        <v>61</v>
+      </c>
+      <c r="E8" s="1">
+        <v>68</v>
+      </c>
+      <c r="F8" s="1">
+        <v>77</v>
+      </c>
+      <c r="G8" s="1">
+        <v>52</v>
+      </c>
+      <c r="H8" s="1">
+        <v>43</v>
+      </c>
+      <c r="I8" s="1">
+        <v>35</v>
+      </c>
+      <c r="J8" s="1">
+        <v>27</v>
+      </c>
+      <c r="K8" s="1">
+        <v>71</v>
+      </c>
+      <c r="L8" s="1">
+        <v>58</v>
+      </c>
+      <c r="M8" s="1">
+        <v>59</v>
+      </c>
+      <c r="N8" s="1">
+        <v>45</v>
+      </c>
+      <c r="O8" s="1">
+        <v>36</v>
+      </c>
+      <c r="P8" s="1">
+        <v>37</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>43</v>
+      </c>
+      <c r="R8" s="1">
+        <v>63</v>
+      </c>
+      <c r="S8" s="1">
+        <v>69</v>
+      </c>
+      <c r="T8" s="1">
+        <v>63</v>
+      </c>
+      <c r="U8" s="1">
+        <v>47</v>
+      </c>
+      <c r="V8" s="1">
+        <v>37</v>
+      </c>
+      <c r="W8" s="1">
+        <v>54</v>
+      </c>
+      <c r="X8" s="1">
+        <v>30</v>
+      </c>
+      <c r="Y8" s="1">
+        <v>58</v>
+      </c>
+      <c r="Z8" s="1">
+        <v>60</v>
+      </c>
+      <c r="AA8" s="1">
+        <v>51</v>
+      </c>
+      <c r="AB8" s="1">
+        <v>58</v>
+      </c>
+      <c r="AC8" s="1">
+        <v>39</v>
+      </c>
+      <c r="AD8" s="1">
+        <v>46</v>
+      </c>
+      <c r="AE8" s="1">
+        <v>29</v>
+      </c>
+      <c r="AF8" s="1">
+        <v>65</v>
+      </c>
+      <c r="AG8" s="1">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9">
+        <v>3</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>4</v>
+      </c>
+      <c r="E9">
+        <v>9</v>
+      </c>
+      <c r="F9">
+        <v>9</v>
+      </c>
+      <c r="G9">
+        <v>7</v>
+      </c>
+      <c r="H9">
+        <v>5</v>
+      </c>
+      <c r="I9">
+        <v>4</v>
+      </c>
+      <c r="K9">
+        <v>4</v>
+      </c>
+      <c r="L9">
+        <v>5</v>
+      </c>
+      <c r="M9">
+        <v>12</v>
+      </c>
+      <c r="N9">
+        <v>71</v>
+      </c>
+      <c r="O9">
+        <v>12</v>
+      </c>
+      <c r="P9">
+        <v>4</v>
+      </c>
+      <c r="R9">
+        <v>9</v>
+      </c>
+      <c r="S9">
+        <v>10</v>
+      </c>
+      <c r="T9">
+        <v>11</v>
+      </c>
+      <c r="U9">
+        <v>14</v>
+      </c>
+      <c r="V9">
+        <v>5</v>
+      </c>
+      <c r="W9">
+        <v>3</v>
+      </c>
+      <c r="Y9">
+        <v>5</v>
+      </c>
+      <c r="Z9">
+        <v>70</v>
+      </c>
+      <c r="AA9">
+        <v>16</v>
+      </c>
+      <c r="AB9">
+        <v>9</v>
+      </c>
+      <c r="AC9">
+        <v>10</v>
+      </c>
+      <c r="AD9">
+        <v>9</v>
+      </c>
+      <c r="AF9">
+        <v>38</v>
+      </c>
+      <c r="AG9">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="1">
+        <v>7</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1">
+        <v>10</v>
+      </c>
+      <c r="E10" s="1">
+        <v>11</v>
+      </c>
+      <c r="F10" s="1">
+        <v>8</v>
+      </c>
+      <c r="G10" s="1">
+        <v>5</v>
+      </c>
+      <c r="H10" s="1">
+        <v>11</v>
+      </c>
+      <c r="I10" s="1">
+        <v>2</v>
+      </c>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1">
+        <v>7</v>
+      </c>
+      <c r="L10" s="1">
+        <v>2</v>
+      </c>
+      <c r="M10" s="1">
+        <v>4</v>
+      </c>
+      <c r="N10" s="1">
+        <v>7</v>
+      </c>
+      <c r="O10" s="1">
+        <v>14</v>
+      </c>
+      <c r="P10" s="1">
+        <v>7</v>
+      </c>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1">
+        <v>8</v>
+      </c>
+      <c r="S10" s="1">
+        <v>2</v>
+      </c>
+      <c r="T10" s="1">
+        <v>4</v>
+      </c>
+      <c r="U10" s="1">
+        <v>9</v>
+      </c>
+      <c r="V10" s="1">
+        <v>8</v>
+      </c>
+      <c r="W10" s="1">
+        <v>6</v>
+      </c>
+      <c r="X10" s="1"/>
+      <c r="Y10" s="1">
+        <v>9</v>
+      </c>
+      <c r="Z10" s="1">
+        <v>11</v>
+      </c>
+      <c r="AA10" s="1">
+        <v>11</v>
+      </c>
+      <c r="AB10" s="1">
+        <v>8</v>
+      </c>
+      <c r="AC10" s="1">
+        <v>5</v>
+      </c>
+      <c r="AD10" s="1">
+        <v>6</v>
+      </c>
+      <c r="AE10" s="1">
+        <v>1</v>
+      </c>
+      <c r="AF10" s="1">
+        <v>12</v>
+      </c>
+      <c r="AG10" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11">
+        <v>4</v>
+      </c>
+      <c r="D11">
+        <v>8</v>
+      </c>
+      <c r="F11">
+        <v>6</v>
+      </c>
+      <c r="G11">
+        <v>3</v>
+      </c>
+      <c r="H11">
+        <v>8</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>7</v>
+      </c>
+      <c r="M11">
+        <v>19</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <v>5</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="R11">
+        <v>5</v>
+      </c>
+      <c r="S11">
+        <v>1</v>
+      </c>
+      <c r="T11">
+        <v>8</v>
+      </c>
+      <c r="V11">
+        <v>20</v>
+      </c>
+      <c r="W11">
+        <v>2</v>
+      </c>
+      <c r="Y11">
+        <v>10</v>
+      </c>
+      <c r="AA11">
+        <v>8</v>
+      </c>
+      <c r="AB11">
+        <v>5</v>
+      </c>
+      <c r="AC11">
+        <v>10</v>
+      </c>
+      <c r="AD11">
+        <v>1</v>
+      </c>
+      <c r="AF11">
+        <v>15</v>
+      </c>
+      <c r="AG11">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1">
+        <v>1</v>
+      </c>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1">
+        <v>3</v>
+      </c>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1">
+        <v>1</v>
+      </c>
+      <c r="U12" s="1"/>
+      <c r="V12" s="1"/>
+      <c r="W12" s="1"/>
+      <c r="X12" s="1"/>
+      <c r="Y12" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="1"/>
+      <c r="AA12" s="1">
+        <v>2</v>
+      </c>
+      <c r="AB12" s="1"/>
+      <c r="AC12" s="1"/>
+      <c r="AD12" s="1"/>
+      <c r="AE12" s="1"/>
+      <c r="AF12" s="1"/>
+      <c r="AG12" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1</v>
+      </c>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1">
+        <v>1</v>
+      </c>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1">
+        <v>1</v>
+      </c>
+      <c r="T14" s="1">
+        <v>1</v>
+      </c>
+      <c r="U14" s="1"/>
+      <c r="V14" s="1"/>
+      <c r="W14" s="1"/>
+      <c r="X14" s="1"/>
+      <c r="Y14" s="1"/>
+      <c r="Z14" s="1"/>
+      <c r="AA14" s="1"/>
+      <c r="AB14" s="1">
+        <v>4</v>
+      </c>
+      <c r="AC14" s="1">
+        <v>2</v>
+      </c>
+      <c r="AD14" s="1">
+        <v>2</v>
+      </c>
+      <c r="AE14" s="1"/>
+      <c r="AF14" s="1"/>
+      <c r="AG14" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="D15">
+        <v>4</v>
+      </c>
+      <c r="E15">
+        <v>7</v>
+      </c>
+      <c r="F15">
+        <v>3</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+      <c r="H15">
+        <v>7</v>
+      </c>
+      <c r="K15">
+        <v>5</v>
+      </c>
+      <c r="L15">
+        <v>2</v>
+      </c>
+      <c r="M15">
+        <v>2</v>
+      </c>
+      <c r="P15">
+        <v>1</v>
+      </c>
+      <c r="R15">
+        <v>6</v>
+      </c>
+      <c r="S15">
+        <v>4</v>
+      </c>
+      <c r="T15">
+        <v>3</v>
+      </c>
+      <c r="U15">
+        <v>4</v>
+      </c>
+      <c r="W15">
+        <v>2</v>
+      </c>
+      <c r="X15">
+        <v>1</v>
+      </c>
+      <c r="Y15">
+        <v>4</v>
+      </c>
+      <c r="Z15">
+        <v>1</v>
+      </c>
+      <c r="AA15">
+        <v>7</v>
+      </c>
+      <c r="AC15">
+        <v>2</v>
+      </c>
+      <c r="AF15">
+        <v>1</v>
+      </c>
+      <c r="AG15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="1">
+        <v>3</v>
+      </c>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1">
+        <v>13</v>
+      </c>
+      <c r="E16" s="1">
+        <v>11</v>
+      </c>
+      <c r="F16" s="1">
+        <v>16</v>
+      </c>
+      <c r="G16" s="1">
+        <v>16</v>
+      </c>
+      <c r="H16" s="1">
+        <v>10</v>
+      </c>
+      <c r="I16" s="1">
+        <v>9</v>
+      </c>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1">
+        <v>11</v>
+      </c>
+      <c r="L16" s="1">
+        <v>13</v>
+      </c>
+      <c r="M16" s="1">
+        <v>19</v>
+      </c>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1">
+        <v>13</v>
+      </c>
+      <c r="P16" s="1">
+        <v>9</v>
+      </c>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1">
+        <v>12</v>
+      </c>
+      <c r="S16" s="1">
+        <v>9</v>
+      </c>
+      <c r="T16" s="1">
+        <v>11</v>
+      </c>
+      <c r="U16" s="1">
+        <v>3</v>
+      </c>
+      <c r="V16" s="1">
+        <v>11</v>
+      </c>
+      <c r="W16" s="1">
+        <v>5</v>
+      </c>
+      <c r="X16" s="1"/>
+      <c r="Y16" s="1">
+        <v>12</v>
+      </c>
+      <c r="Z16" s="1">
+        <v>15</v>
+      </c>
+      <c r="AA16" s="1">
+        <v>10</v>
+      </c>
+      <c r="AB16" s="1">
+        <v>10</v>
+      </c>
+      <c r="AC16" s="1">
+        <v>8</v>
+      </c>
+      <c r="AD16" s="1">
+        <v>5</v>
+      </c>
+      <c r="AE16" s="1"/>
+      <c r="AF16" s="1">
+        <v>12</v>
+      </c>
+      <c r="AG16" s="1">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>6</v>
+      </c>
+      <c r="E17">
+        <v>7</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17">
+        <v>6</v>
+      </c>
+      <c r="H17">
+        <v>6</v>
+      </c>
+      <c r="K17">
+        <v>5</v>
+      </c>
+      <c r="L17">
+        <v>3</v>
+      </c>
+      <c r="M17">
+        <v>2</v>
+      </c>
+      <c r="O17">
+        <v>7</v>
+      </c>
+      <c r="P17">
+        <v>4</v>
+      </c>
+      <c r="R17">
+        <v>5</v>
+      </c>
+      <c r="S17">
+        <v>9</v>
+      </c>
+      <c r="T17">
+        <v>3</v>
+      </c>
+      <c r="U17">
+        <v>4</v>
+      </c>
+      <c r="V17">
+        <v>1</v>
+      </c>
+      <c r="W17">
+        <v>3</v>
+      </c>
+      <c r="X17">
+        <v>1</v>
+      </c>
+      <c r="Y17">
+        <v>6</v>
+      </c>
+      <c r="Z17">
+        <v>2</v>
+      </c>
+      <c r="AA17">
+        <v>2</v>
+      </c>
+      <c r="AB17">
+        <v>2</v>
+      </c>
+      <c r="AD17">
+        <v>2</v>
+      </c>
+      <c r="AF17">
+        <v>3</v>
+      </c>
+      <c r="AG17">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="1">
+        <v>4</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1">
+        <v>5</v>
+      </c>
+      <c r="E18" s="1">
+        <v>3</v>
+      </c>
+      <c r="F18" s="1">
+        <v>7</v>
+      </c>
+      <c r="G18" s="1">
+        <v>1</v>
+      </c>
+      <c r="H18" s="1">
+        <v>3</v>
+      </c>
+      <c r="I18" s="1">
+        <v>5</v>
+      </c>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1">
+        <v>5</v>
+      </c>
+      <c r="L18" s="1">
+        <v>10</v>
+      </c>
+      <c r="M18" s="1">
+        <v>5</v>
+      </c>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1">
+        <v>4</v>
+      </c>
+      <c r="P18" s="1">
+        <v>8</v>
+      </c>
+      <c r="Q18" s="1"/>
+      <c r="R18" s="1">
+        <v>6</v>
+      </c>
+      <c r="S18" s="1">
+        <v>7</v>
+      </c>
+      <c r="T18" s="1">
+        <v>4</v>
+      </c>
+      <c r="U18" s="1">
+        <v>2</v>
+      </c>
+      <c r="V18" s="1">
+        <v>4</v>
+      </c>
+      <c r="W18" s="1">
+        <v>2</v>
+      </c>
+      <c r="X18" s="1"/>
+      <c r="Y18" s="1">
+        <v>7</v>
+      </c>
+      <c r="Z18" s="1">
+        <v>7</v>
+      </c>
+      <c r="AA18" s="1">
+        <v>3</v>
+      </c>
+      <c r="AB18" s="1">
+        <v>5</v>
+      </c>
+      <c r="AC18" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD18" s="1">
+        <v>4</v>
+      </c>
+      <c r="AE18" s="1"/>
+      <c r="AF18" s="1">
+        <v>7</v>
+      </c>
+      <c r="AG18" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19">
+        <v>20</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <v>27</v>
+      </c>
+      <c r="E19">
+        <v>24</v>
+      </c>
+      <c r="F19">
+        <v>29</v>
+      </c>
+      <c r="G19">
+        <v>21</v>
+      </c>
+      <c r="H19">
+        <v>20</v>
+      </c>
+      <c r="I19">
+        <v>15</v>
+      </c>
+      <c r="J19">
+        <v>4</v>
+      </c>
+      <c r="K19">
+        <v>34</v>
+      </c>
+      <c r="L19">
+        <v>16</v>
+      </c>
+      <c r="M19">
+        <v>16</v>
+      </c>
+      <c r="N19">
+        <v>18</v>
+      </c>
+      <c r="O19">
+        <v>23</v>
+      </c>
+      <c r="P19">
+        <v>23</v>
+      </c>
+      <c r="Q19">
+        <v>3</v>
+      </c>
+      <c r="R19">
+        <v>29</v>
+      </c>
+      <c r="S19">
+        <v>23</v>
+      </c>
+      <c r="T19">
+        <v>26</v>
+      </c>
+      <c r="U19">
+        <v>24</v>
+      </c>
+      <c r="V19">
+        <v>19</v>
+      </c>
+      <c r="W19">
+        <v>16</v>
+      </c>
+      <c r="X19">
+        <v>3</v>
+      </c>
+      <c r="Y19">
+        <v>32</v>
+      </c>
+      <c r="Z19">
+        <v>18</v>
+      </c>
+      <c r="AA19">
+        <v>22</v>
+      </c>
+      <c r="AB19">
+        <v>11</v>
+      </c>
+      <c r="AC19">
+        <v>22</v>
+      </c>
+      <c r="AD19">
+        <v>11</v>
+      </c>
+      <c r="AE19">
+        <v>4</v>
+      </c>
+      <c r="AF19">
+        <v>29</v>
+      </c>
+      <c r="AG19">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="1">
+        <v>2</v>
+      </c>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1">
+        <v>3</v>
+      </c>
+      <c r="F20" s="1">
+        <v>5</v>
+      </c>
+      <c r="G20" s="1">
+        <v>1</v>
+      </c>
+      <c r="H20" s="1">
+        <v>1</v>
+      </c>
+      <c r="I20" s="1">
+        <v>4</v>
+      </c>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1">
+        <v>1</v>
+      </c>
+      <c r="L20" s="1">
+        <v>6</v>
+      </c>
+      <c r="M20" s="1">
+        <v>5</v>
+      </c>
+      <c r="N20" s="1">
+        <v>2</v>
+      </c>
+      <c r="O20" s="1">
+        <v>3</v>
+      </c>
+      <c r="P20" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="1"/>
+      <c r="S20" s="1">
+        <v>5</v>
+      </c>
+      <c r="T20" s="1"/>
+      <c r="U20" s="1">
+        <v>4</v>
+      </c>
+      <c r="V20" s="1">
+        <v>1</v>
+      </c>
+      <c r="W20" s="1">
+        <v>1</v>
+      </c>
+      <c r="X20" s="1"/>
+      <c r="Y20" s="1"/>
+      <c r="Z20" s="1">
+        <v>4</v>
+      </c>
+      <c r="AA20" s="1">
+        <v>3</v>
+      </c>
+      <c r="AB20" s="1">
+        <v>3</v>
+      </c>
+      <c r="AC20" s="1">
+        <v>3</v>
+      </c>
+      <c r="AD20" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE20" s="1"/>
+      <c r="AF20" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG20" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21">
+        <v>8</v>
+      </c>
+      <c r="C21">
+        <v>9</v>
+      </c>
+      <c r="D21">
+        <v>37</v>
+      </c>
+      <c r="E21">
+        <v>27</v>
+      </c>
+      <c r="F21">
+        <v>63</v>
+      </c>
+      <c r="G21">
+        <v>21</v>
+      </c>
+      <c r="H21">
+        <v>16</v>
+      </c>
+      <c r="I21">
+        <v>18</v>
+      </c>
+      <c r="J21">
+        <v>6</v>
+      </c>
+      <c r="K21">
+        <v>34</v>
+      </c>
+      <c r="L21">
+        <v>26</v>
+      </c>
+      <c r="M21">
+        <v>29</v>
+      </c>
+      <c r="N21">
+        <v>27</v>
+      </c>
+      <c r="O21">
+        <v>9</v>
+      </c>
+      <c r="P21">
+        <v>13</v>
+      </c>
+      <c r="Q21">
+        <v>8</v>
+      </c>
+      <c r="R21">
+        <v>35</v>
+      </c>
+      <c r="S21">
+        <v>29</v>
+      </c>
+      <c r="T21">
+        <v>22</v>
+      </c>
+      <c r="U21">
+        <v>28</v>
+      </c>
+      <c r="V21">
+        <v>18</v>
+      </c>
+      <c r="W21">
+        <v>16</v>
+      </c>
+      <c r="X21">
+        <v>10</v>
+      </c>
+      <c r="Y21">
+        <v>28</v>
+      </c>
+      <c r="Z21">
+        <v>28</v>
+      </c>
+      <c r="AA21">
+        <v>24</v>
+      </c>
+      <c r="AB21">
+        <v>20</v>
+      </c>
+      <c r="AC21">
+        <v>8</v>
+      </c>
+      <c r="AD21">
+        <v>10</v>
+      </c>
+      <c r="AE21">
+        <v>2</v>
+      </c>
+      <c r="AF21">
+        <v>33</v>
+      </c>
+      <c r="AG21">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1">
+        <v>1</v>
+      </c>
+      <c r="F22" s="1">
+        <v>1</v>
+      </c>
+      <c r="G22" s="1">
+        <v>1</v>
+      </c>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1">
+        <v>1</v>
+      </c>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1">
+        <v>1</v>
+      </c>
+      <c r="N22" s="1">
+        <v>1</v>
+      </c>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1"/>
+      <c r="R22" s="1">
+        <v>1</v>
+      </c>
+      <c r="S22" s="1"/>
+      <c r="T22" s="1">
+        <v>2</v>
+      </c>
+      <c r="U22" s="1">
+        <v>1</v>
+      </c>
+      <c r="V22" s="1">
+        <v>17</v>
+      </c>
+      <c r="W22" s="1"/>
+      <c r="X22" s="1"/>
+      <c r="Y22" s="1"/>
+      <c r="Z22" s="1">
+        <v>2</v>
+      </c>
+      <c r="AA22" s="1"/>
+      <c r="AB22" s="1"/>
+      <c r="AC22" s="1">
+        <v>3</v>
+      </c>
+      <c r="AD22" s="1"/>
+      <c r="AE22" s="1"/>
+      <c r="AF22" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG22" s="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23">
+        <v>9</v>
+      </c>
+      <c r="D23">
+        <v>31</v>
+      </c>
+      <c r="E23">
+        <v>30</v>
+      </c>
+      <c r="F23">
+        <v>28</v>
+      </c>
+      <c r="G23">
+        <v>37</v>
+      </c>
+      <c r="H23">
+        <v>16</v>
+      </c>
+      <c r="I23">
+        <v>12</v>
+      </c>
+      <c r="K23">
+        <v>22</v>
+      </c>
+      <c r="L23">
+        <v>33</v>
+      </c>
+      <c r="M23">
+        <v>32</v>
+      </c>
+      <c r="N23">
+        <v>25</v>
+      </c>
+      <c r="O23">
+        <v>30</v>
+      </c>
+      <c r="P23">
+        <v>10</v>
+      </c>
+      <c r="R23">
+        <v>29</v>
+      </c>
+      <c r="S23">
+        <v>26</v>
+      </c>
+      <c r="T23">
+        <v>30</v>
+      </c>
+      <c r="U23">
+        <v>32</v>
+      </c>
+      <c r="V23">
+        <v>18</v>
+      </c>
+      <c r="W23">
+        <v>11</v>
+      </c>
+      <c r="Y23">
+        <v>25</v>
+      </c>
+      <c r="Z23">
+        <v>32</v>
+      </c>
+      <c r="AA23">
+        <v>26</v>
+      </c>
+      <c r="AB23">
+        <v>26</v>
+      </c>
+      <c r="AC23">
+        <v>30</v>
+      </c>
+      <c r="AD23">
+        <v>8</v>
+      </c>
+      <c r="AE23">
+        <v>1</v>
+      </c>
+      <c r="AF23">
+        <v>36</v>
+      </c>
+      <c r="AG23">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="1">
+        <v>5</v>
+      </c>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1">
+        <v>7</v>
+      </c>
+      <c r="F24" s="1">
+        <v>4</v>
+      </c>
+      <c r="G24" s="1">
+        <v>5</v>
+      </c>
+      <c r="H24" s="1">
+        <v>7</v>
+      </c>
+      <c r="I24" s="1">
+        <v>4</v>
+      </c>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1">
+        <v>10</v>
+      </c>
+      <c r="M24" s="1">
+        <v>5</v>
+      </c>
+      <c r="N24" s="1">
+        <v>3</v>
+      </c>
+      <c r="O24" s="1">
+        <v>10</v>
+      </c>
+      <c r="P24" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="1"/>
+      <c r="S24" s="1">
+        <v>8</v>
+      </c>
+      <c r="T24" s="1">
+        <v>5</v>
+      </c>
+      <c r="U24" s="1">
+        <v>2</v>
+      </c>
+      <c r="V24" s="1">
+        <v>9</v>
+      </c>
+      <c r="W24" s="1">
+        <v>3</v>
+      </c>
+      <c r="X24" s="1"/>
+      <c r="Y24" s="1"/>
+      <c r="Z24" s="1">
+        <v>8</v>
+      </c>
+      <c r="AA24" s="1">
+        <v>6</v>
+      </c>
+      <c r="AB24" s="1">
+        <v>6</v>
+      </c>
+      <c r="AC24" s="1">
+        <v>6</v>
+      </c>
+      <c r="AD24" s="1">
+        <v>4</v>
+      </c>
+      <c r="AE24" s="1"/>
+      <c r="AF24" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG24" s="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25">
+        <v>12</v>
+      </c>
+      <c r="C25">
+        <v>3</v>
+      </c>
+      <c r="D25">
+        <v>47</v>
+      </c>
+      <c r="E25">
+        <v>31</v>
+      </c>
+      <c r="F25">
+        <v>35</v>
+      </c>
+      <c r="G25">
+        <v>54</v>
+      </c>
+      <c r="H25">
+        <v>33</v>
+      </c>
+      <c r="I25">
+        <v>21</v>
+      </c>
+      <c r="J25">
+        <v>1</v>
+      </c>
+      <c r="K25">
+        <v>40</v>
+      </c>
+      <c r="L25">
+        <v>37</v>
+      </c>
+      <c r="M25">
+        <v>26</v>
+      </c>
+      <c r="N25">
+        <v>38</v>
+      </c>
+      <c r="O25">
+        <v>37</v>
+      </c>
+      <c r="P25">
+        <v>21</v>
+      </c>
+      <c r="Q25">
+        <v>5</v>
+      </c>
+      <c r="R25">
+        <v>27</v>
+      </c>
+      <c r="S25">
+        <v>34</v>
+      </c>
+      <c r="T25">
+        <v>28</v>
+      </c>
+      <c r="U25">
+        <v>51</v>
+      </c>
+      <c r="V25">
+        <v>27</v>
+      </c>
+      <c r="W25">
+        <v>27</v>
+      </c>
+      <c r="X25">
+        <v>4</v>
+      </c>
+      <c r="Y25">
+        <v>35</v>
+      </c>
+      <c r="Z25">
+        <v>34</v>
+      </c>
+      <c r="AA25">
+        <v>30</v>
+      </c>
+      <c r="AB25">
+        <v>39</v>
+      </c>
+      <c r="AC25">
+        <v>38</v>
+      </c>
+      <c r="AD25">
+        <v>20</v>
+      </c>
+      <c r="AE25">
+        <v>3</v>
+      </c>
+      <c r="AF25">
+        <v>39</v>
+      </c>
+      <c r="AG25">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" s="1">
+        <v>101</v>
+      </c>
+      <c r="C26" s="1">
+        <v>60</v>
+      </c>
+      <c r="D26" s="1">
+        <v>150</v>
+      </c>
+      <c r="E26" s="1">
+        <v>131</v>
+      </c>
+      <c r="F26" s="1">
+        <v>119</v>
+      </c>
+      <c r="G26" s="1">
+        <v>116</v>
+      </c>
+      <c r="H26" s="1">
+        <v>90</v>
+      </c>
+      <c r="I26" s="1">
+        <v>108</v>
+      </c>
+      <c r="J26" s="1">
+        <v>45</v>
+      </c>
+      <c r="K26" s="1">
+        <v>122</v>
+      </c>
+      <c r="L26" s="1">
+        <v>136</v>
+      </c>
+      <c r="M26" s="1">
+        <v>113</v>
+      </c>
+      <c r="N26" s="1">
+        <v>123</v>
+      </c>
+      <c r="O26" s="1">
+        <v>18</v>
+      </c>
+      <c r="P26" s="1">
+        <v>104</v>
+      </c>
+      <c r="Q26" s="1">
+        <v>64</v>
+      </c>
+      <c r="R26" s="1">
+        <v>124</v>
+      </c>
+      <c r="S26" s="1">
+        <v>107</v>
+      </c>
+      <c r="T26" s="1">
+        <v>125</v>
+      </c>
+      <c r="U26" s="1">
+        <v>124</v>
+      </c>
+      <c r="V26" s="1">
+        <v>95</v>
+      </c>
+      <c r="W26" s="1">
+        <v>94</v>
+      </c>
+      <c r="X26" s="1">
+        <v>59</v>
+      </c>
+      <c r="Y26" s="1">
+        <v>125</v>
+      </c>
+      <c r="Z26" s="1">
+        <v>120</v>
+      </c>
+      <c r="AA26" s="1">
+        <v>107</v>
+      </c>
+      <c r="AB26" s="1">
+        <v>122</v>
+      </c>
+      <c r="AC26" s="1">
+        <v>103</v>
+      </c>
+      <c r="AD26" s="1">
+        <v>95</v>
+      </c>
+      <c r="AE26" s="1">
+        <v>46</v>
+      </c>
+      <c r="AF26" s="1">
+        <v>116</v>
+      </c>
+      <c r="AG26" s="1">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27">
+        <v>5</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>11</v>
+      </c>
+      <c r="E27">
+        <v>10</v>
+      </c>
+      <c r="F27">
+        <v>8</v>
+      </c>
+      <c r="G27">
+        <v>10</v>
+      </c>
+      <c r="H27">
+        <v>9</v>
+      </c>
+      <c r="I27">
+        <v>11</v>
+      </c>
+      <c r="J27">
+        <v>1</v>
+      </c>
+      <c r="K27">
+        <v>9</v>
+      </c>
+      <c r="L27">
+        <v>5</v>
+      </c>
+      <c r="M27">
+        <v>5</v>
+      </c>
+      <c r="N27">
+        <v>9</v>
+      </c>
+      <c r="O27">
+        <v>10</v>
+      </c>
+      <c r="P27">
+        <v>8</v>
+      </c>
+      <c r="Q27">
+        <v>2</v>
+      </c>
+      <c r="R27">
+        <v>11</v>
+      </c>
+      <c r="S27">
+        <v>8</v>
+      </c>
+      <c r="T27">
+        <v>6</v>
+      </c>
+      <c r="U27">
+        <v>6</v>
+      </c>
+      <c r="V27">
+        <v>7</v>
+      </c>
+      <c r="W27">
+        <v>3</v>
+      </c>
+      <c r="Y27">
+        <v>6</v>
+      </c>
+      <c r="Z27">
+        <v>6</v>
+      </c>
+      <c r="AA27">
+        <v>11</v>
+      </c>
+      <c r="AB27">
+        <v>11</v>
+      </c>
+      <c r="AC27">
+        <v>8</v>
+      </c>
+      <c r="AD27">
+        <v>9</v>
+      </c>
+      <c r="AE27">
+        <v>1</v>
+      </c>
+      <c r="AF27">
+        <v>9</v>
+      </c>
+      <c r="AG27">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
+      <c r="R28" s="1"/>
+      <c r="S28" s="1"/>
+      <c r="T28" s="1"/>
+      <c r="U28" s="1"/>
+      <c r="V28" s="1"/>
+      <c r="W28" s="1"/>
+      <c r="X28" s="1"/>
+      <c r="Y28" s="1"/>
+      <c r="Z28" s="1"/>
+      <c r="AA28" s="1"/>
+      <c r="AB28" s="1"/>
+      <c r="AC28" s="1"/>
+      <c r="AD28" s="1"/>
+      <c r="AE28" s="1"/>
+      <c r="AF28" s="1"/>
+      <c r="AG28" s="1"/>
+    </row>
+    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29">
+        <v>8</v>
+      </c>
+      <c r="D29">
+        <v>7</v>
+      </c>
+      <c r="E29">
+        <v>7</v>
+      </c>
+      <c r="F29">
+        <v>16</v>
+      </c>
+      <c r="G29">
+        <v>5</v>
+      </c>
+      <c r="I29">
+        <v>7</v>
+      </c>
+      <c r="K29">
+        <v>13</v>
+      </c>
+      <c r="L29">
+        <v>12</v>
+      </c>
+      <c r="M29">
+        <v>6</v>
+      </c>
+      <c r="N29">
+        <v>6</v>
+      </c>
+      <c r="P29">
+        <v>7</v>
+      </c>
+      <c r="R29">
+        <v>8</v>
+      </c>
+      <c r="S29">
+        <v>6</v>
+      </c>
+      <c r="T29">
+        <v>5</v>
+      </c>
+      <c r="U29">
+        <v>13</v>
+      </c>
+      <c r="W29">
+        <v>6</v>
+      </c>
+      <c r="X29">
+        <v>2</v>
+      </c>
+      <c r="Y29">
+        <v>8</v>
+      </c>
+      <c r="Z29">
+        <v>12</v>
+      </c>
+      <c r="AA29">
+        <v>11</v>
+      </c>
+      <c r="AB29">
+        <v>8</v>
+      </c>
+      <c r="AC29">
+        <v>1</v>
+      </c>
+      <c r="AD29">
+        <v>5</v>
+      </c>
+      <c r="AE29">
+        <v>2</v>
+      </c>
+      <c r="AF29">
+        <v>9</v>
+      </c>
+      <c r="AG29">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="1">
+        <v>3</v>
+      </c>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1">
+        <v>5</v>
+      </c>
+      <c r="E30" s="1">
+        <v>10</v>
+      </c>
+      <c r="F30" s="1">
+        <v>7</v>
+      </c>
+      <c r="G30" s="1">
+        <v>3</v>
+      </c>
+      <c r="H30" s="1">
+        <v>10</v>
+      </c>
+      <c r="I30" s="1">
+        <v>1</v>
+      </c>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1">
+        <v>5</v>
+      </c>
+      <c r="L30" s="1">
+        <v>5</v>
+      </c>
+      <c r="M30" s="1">
+        <v>7</v>
+      </c>
+      <c r="N30" s="1">
+        <v>5</v>
+      </c>
+      <c r="O30" s="1">
+        <v>9</v>
+      </c>
+      <c r="P30" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q30" s="1">
+        <v>2</v>
+      </c>
+      <c r="R30" s="1">
+        <v>13</v>
+      </c>
+      <c r="S30" s="1">
+        <v>11</v>
+      </c>
+      <c r="T30" s="1">
+        <v>7</v>
+      </c>
+      <c r="U30" s="1">
+        <v>8</v>
+      </c>
+      <c r="V30" s="1">
+        <v>6</v>
+      </c>
+      <c r="W30" s="1">
+        <v>1</v>
+      </c>
+      <c r="X30" s="1"/>
+      <c r="Y30" s="1">
+        <v>7</v>
+      </c>
+      <c r="Z30" s="1">
+        <v>7</v>
+      </c>
+      <c r="AA30" s="1">
+        <v>4</v>
+      </c>
+      <c r="AB30" s="1">
+        <v>9</v>
+      </c>
+      <c r="AC30" s="1">
+        <v>8</v>
+      </c>
+      <c r="AD30" s="1">
+        <v>3</v>
+      </c>
+      <c r="AE30" s="1">
+        <v>1</v>
+      </c>
+      <c r="AF30" s="1">
+        <v>10</v>
+      </c>
+      <c r="AG30" s="1">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31">
+        <v>12</v>
+      </c>
+      <c r="D31">
+        <v>33</v>
+      </c>
+      <c r="E31">
+        <v>29</v>
+      </c>
+      <c r="F31">
+        <v>18</v>
+      </c>
+      <c r="G31">
+        <v>20</v>
+      </c>
+      <c r="H31">
+        <v>23</v>
+      </c>
+      <c r="I31">
+        <v>16</v>
+      </c>
+      <c r="K31">
+        <v>23</v>
+      </c>
+      <c r="L31">
+        <v>30</v>
+      </c>
+      <c r="M31">
+        <v>20</v>
+      </c>
+      <c r="N31">
+        <v>21</v>
+      </c>
+      <c r="O31">
+        <v>20</v>
+      </c>
+      <c r="P31">
+        <v>10</v>
+      </c>
+      <c r="Q31">
+        <v>2</v>
+      </c>
+      <c r="R31">
+        <v>20</v>
+      </c>
+      <c r="S31">
+        <v>14</v>
+      </c>
+      <c r="T31">
+        <v>21</v>
+      </c>
+      <c r="U31">
+        <v>14</v>
+      </c>
+      <c r="V31">
+        <v>21</v>
+      </c>
+      <c r="W31">
+        <v>8</v>
+      </c>
+      <c r="Y31">
+        <v>18</v>
+      </c>
+      <c r="Z31">
+        <v>8</v>
+      </c>
+      <c r="AA31">
+        <v>20</v>
+      </c>
+      <c r="AB31">
+        <v>19</v>
+      </c>
+      <c r="AC31">
+        <v>19</v>
+      </c>
+      <c r="AD31">
+        <v>15</v>
+      </c>
+      <c r="AE31">
+        <v>2</v>
+      </c>
+      <c r="AF31">
+        <v>31</v>
+      </c>
+      <c r="AG31">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="1">
+        <v>1</v>
+      </c>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1">
+        <v>3</v>
+      </c>
+      <c r="E32" s="1">
+        <v>3</v>
+      </c>
+      <c r="F32" s="1">
+        <v>1</v>
+      </c>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1">
+        <v>1</v>
+      </c>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1">
+        <v>1</v>
+      </c>
+      <c r="M32" s="1">
+        <v>2</v>
+      </c>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1">
+        <v>2</v>
+      </c>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1"/>
+      <c r="R32" s="1"/>
+      <c r="S32" s="1"/>
+      <c r="T32" s="1">
+        <v>2</v>
+      </c>
+      <c r="U32" s="1">
+        <v>1</v>
+      </c>
+      <c r="V32" s="1">
+        <v>1</v>
+      </c>
+      <c r="W32" s="1"/>
+      <c r="X32" s="1"/>
+      <c r="Y32" s="1"/>
+      <c r="Z32" s="1">
+        <v>2</v>
+      </c>
+      <c r="AA32" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB32" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC32" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD32" s="1"/>
+      <c r="AE32" s="1"/>
+      <c r="AF32" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG32" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="E33">
+        <v>7</v>
+      </c>
+      <c r="F33">
+        <v>2</v>
+      </c>
+      <c r="G33">
+        <v>5</v>
+      </c>
+      <c r="H33">
+        <v>4</v>
+      </c>
+      <c r="I33">
+        <v>1</v>
+      </c>
+      <c r="K33">
+        <v>1</v>
+      </c>
+      <c r="L33">
+        <v>6</v>
+      </c>
+      <c r="M33">
+        <v>2</v>
+      </c>
+      <c r="N33">
+        <v>1</v>
+      </c>
+      <c r="O33">
+        <v>5</v>
+      </c>
+      <c r="S33">
+        <v>6</v>
+      </c>
+      <c r="T33">
+        <v>5</v>
+      </c>
+      <c r="U33">
+        <v>4</v>
+      </c>
+      <c r="V33">
+        <v>4</v>
+      </c>
+      <c r="W33">
+        <v>1</v>
+      </c>
+      <c r="Z33">
+        <v>5</v>
+      </c>
+      <c r="AA33">
+        <v>3</v>
+      </c>
+      <c r="AB33">
+        <v>3</v>
+      </c>
+      <c r="AC33">
+        <v>5</v>
+      </c>
+      <c r="AD33">
+        <v>2</v>
+      </c>
+      <c r="AG33">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="1">
+        <v>8</v>
+      </c>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1">
+        <v>28</v>
+      </c>
+      <c r="E34" s="1">
+        <v>31</v>
+      </c>
+      <c r="F34" s="1">
+        <v>24</v>
+      </c>
+      <c r="G34" s="1">
+        <v>30</v>
+      </c>
+      <c r="H34" s="1">
+        <v>24</v>
+      </c>
+      <c r="I34" s="1">
+        <v>20</v>
+      </c>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1">
+        <v>33</v>
+      </c>
+      <c r="L34" s="1">
+        <v>22</v>
+      </c>
+      <c r="M34" s="1">
+        <v>21</v>
+      </c>
+      <c r="N34" s="1">
+        <v>28</v>
+      </c>
+      <c r="O34" s="1">
+        <v>21</v>
+      </c>
+      <c r="P34" s="1">
+        <v>15</v>
+      </c>
+      <c r="Q34" s="1"/>
+      <c r="R34" s="1">
+        <v>33</v>
+      </c>
+      <c r="S34" s="1">
+        <v>27</v>
+      </c>
+      <c r="T34" s="1">
+        <v>27</v>
+      </c>
+      <c r="U34" s="1">
+        <v>22</v>
+      </c>
+      <c r="V34" s="1">
+        <v>14</v>
+      </c>
+      <c r="W34" s="1">
+        <v>18</v>
+      </c>
+      <c r="X34" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y34" s="1">
+        <v>37</v>
+      </c>
+      <c r="Z34" s="1">
+        <v>21</v>
+      </c>
+      <c r="AA34" s="1">
+        <v>21</v>
+      </c>
+      <c r="AB34" s="1">
+        <v>26</v>
+      </c>
+      <c r="AC34" s="1">
+        <v>16</v>
+      </c>
+      <c r="AD34" s="1">
+        <v>17</v>
+      </c>
+      <c r="AE34" s="1"/>
+      <c r="AF34" s="1">
+        <v>35</v>
+      </c>
+      <c r="AG34" s="1">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="35" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35">
+        <v>8</v>
+      </c>
+      <c r="D35">
+        <v>28</v>
+      </c>
+      <c r="E35">
+        <v>22</v>
+      </c>
+      <c r="F35">
+        <v>20</v>
+      </c>
+      <c r="G35">
+        <v>19</v>
+      </c>
+      <c r="H35">
+        <v>18</v>
+      </c>
+      <c r="I35">
+        <v>7</v>
+      </c>
+      <c r="K35">
+        <v>24</v>
+      </c>
+      <c r="L35">
+        <v>13</v>
+      </c>
+      <c r="M35">
+        <v>20</v>
+      </c>
+      <c r="N35">
+        <v>15</v>
+      </c>
+      <c r="O35">
+        <v>24</v>
+      </c>
+      <c r="P35">
+        <v>10</v>
+      </c>
+      <c r="R35">
+        <v>32</v>
+      </c>
+      <c r="S35">
+        <v>23</v>
+      </c>
+      <c r="T35">
+        <v>13</v>
+      </c>
+      <c r="U35">
+        <v>16</v>
+      </c>
+      <c r="V35">
+        <v>19</v>
+      </c>
+      <c r="W35">
+        <v>12</v>
+      </c>
+      <c r="Y35">
+        <v>37</v>
+      </c>
+      <c r="Z35">
+        <v>22</v>
+      </c>
+      <c r="AA35">
+        <v>15</v>
+      </c>
+      <c r="AB35">
+        <v>20</v>
+      </c>
+      <c r="AC35">
+        <v>20</v>
+      </c>
+      <c r="AD35">
+        <v>13</v>
+      </c>
+      <c r="AF35">
+        <v>28</v>
+      </c>
+      <c r="AG35">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" s="1">
+        <v>4</v>
+      </c>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1">
+        <v>22</v>
+      </c>
+      <c r="E36" s="1">
+        <v>11</v>
+      </c>
+      <c r="F36" s="1">
+        <v>10</v>
+      </c>
+      <c r="G36" s="1">
+        <v>13</v>
+      </c>
+      <c r="H36" s="1">
+        <v>5</v>
+      </c>
+      <c r="I36" s="1">
+        <v>1</v>
+      </c>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1">
+        <v>8</v>
+      </c>
+      <c r="L36" s="1">
+        <v>16</v>
+      </c>
+      <c r="M36" s="1">
+        <v>12</v>
+      </c>
+      <c r="N36" s="1">
+        <v>15</v>
+      </c>
+      <c r="O36" s="1">
+        <v>13</v>
+      </c>
+      <c r="P36" s="1">
+        <v>4</v>
+      </c>
+      <c r="Q36" s="1"/>
+      <c r="R36" s="1">
+        <v>20</v>
+      </c>
+      <c r="S36" s="1">
+        <v>9</v>
+      </c>
+      <c r="T36" s="1">
+        <v>12</v>
+      </c>
+      <c r="U36" s="1">
+        <v>9</v>
+      </c>
+      <c r="V36" s="1">
+        <v>15</v>
+      </c>
+      <c r="W36" s="1">
+        <v>5</v>
+      </c>
+      <c r="X36" s="1"/>
+      <c r="Y36" s="1">
+        <v>10</v>
+      </c>
+      <c r="Z36" s="1">
+        <v>24</v>
+      </c>
+      <c r="AA36" s="1">
+        <v>7</v>
+      </c>
+      <c r="AB36" s="1">
+        <v>7</v>
+      </c>
+      <c r="AC36" s="1">
+        <v>4</v>
+      </c>
+      <c r="AD36" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE36" s="1"/>
+      <c r="AF36" s="1"/>
+      <c r="AG36" s="1">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>46</v>
+      </c>
+      <c r="B37">
+        <v>30</v>
+      </c>
+      <c r="C37">
+        <v>5</v>
+      </c>
+      <c r="D37">
+        <v>73</v>
+      </c>
+      <c r="E37">
+        <v>76</v>
+      </c>
+      <c r="F37">
+        <v>74</v>
+      </c>
+      <c r="G37">
+        <v>68</v>
+      </c>
+      <c r="H37">
+        <v>51</v>
+      </c>
+      <c r="I37">
+        <v>29</v>
+      </c>
+      <c r="J37">
+        <v>4</v>
+      </c>
+      <c r="K37">
+        <v>95</v>
+      </c>
+      <c r="L37">
+        <v>73</v>
+      </c>
+      <c r="M37">
+        <v>74</v>
+      </c>
+      <c r="N37">
+        <v>72</v>
+      </c>
+      <c r="O37">
+        <v>56</v>
+      </c>
+      <c r="P37">
+        <v>25</v>
+      </c>
+      <c r="Q37">
+        <v>3</v>
+      </c>
+      <c r="R37">
+        <v>82</v>
+      </c>
+      <c r="S37">
+        <v>53</v>
+      </c>
+      <c r="T37">
+        <v>63</v>
+      </c>
+      <c r="U37">
+        <v>66</v>
+      </c>
+      <c r="V37">
+        <v>58</v>
+      </c>
+      <c r="W37">
+        <v>29</v>
+      </c>
+      <c r="X37">
+        <v>7</v>
+      </c>
+      <c r="Y37">
+        <v>73</v>
+      </c>
+      <c r="Z37">
+        <v>67</v>
+      </c>
+      <c r="AA37">
+        <v>70</v>
+      </c>
+      <c r="AB37">
+        <v>55</v>
+      </c>
+      <c r="AC37">
+        <v>64</v>
+      </c>
+      <c r="AD37">
+        <v>36</v>
+      </c>
+      <c r="AE37">
+        <v>8</v>
+      </c>
+      <c r="AF37">
+        <v>83</v>
+      </c>
+      <c r="AG37">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B38" s="1">
+        <v>4</v>
+      </c>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1">
+        <v>11</v>
+      </c>
+      <c r="E38" s="1">
+        <v>9</v>
+      </c>
+      <c r="F38" s="1">
+        <v>12</v>
+      </c>
+      <c r="G38" s="1">
+        <v>12</v>
+      </c>
+      <c r="H38" s="1">
+        <v>15</v>
+      </c>
+      <c r="I38" s="1">
+        <v>6</v>
+      </c>
+      <c r="J38" s="1">
+        <v>1</v>
+      </c>
+      <c r="K38" s="1">
+        <v>14</v>
+      </c>
+      <c r="L38" s="1">
+        <v>12</v>
+      </c>
+      <c r="M38" s="1">
+        <v>11</v>
+      </c>
+      <c r="N38" s="1">
+        <v>9</v>
+      </c>
+      <c r="O38" s="1">
+        <v>10</v>
+      </c>
+      <c r="P38" s="1">
+        <v>4</v>
+      </c>
+      <c r="Q38" s="1"/>
+      <c r="R38" s="1">
+        <v>14</v>
+      </c>
+      <c r="S38" s="1">
+        <v>23</v>
+      </c>
+      <c r="T38" s="1">
+        <v>15</v>
+      </c>
+      <c r="U38" s="1">
+        <v>19</v>
+      </c>
+      <c r="V38" s="1">
+        <v>8</v>
+      </c>
+      <c r="W38" s="1">
+        <v>11</v>
+      </c>
+      <c r="X38" s="1"/>
+      <c r="Y38" s="1">
+        <v>14</v>
+      </c>
+      <c r="Z38" s="1">
+        <v>12</v>
+      </c>
+      <c r="AA38" s="1">
+        <v>8</v>
+      </c>
+      <c r="AB38" s="1">
+        <v>11</v>
+      </c>
+      <c r="AC38" s="1">
+        <v>12</v>
+      </c>
+      <c r="AD38" s="1">
+        <v>13</v>
+      </c>
+      <c r="AE38" s="1">
+        <v>1</v>
+      </c>
+      <c r="AF38" s="1">
+        <v>10</v>
+      </c>
+      <c r="AG38" s="1">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39">
+        <v>33</v>
+      </c>
+      <c r="C39">
+        <v>2</v>
+      </c>
+      <c r="D39">
+        <v>72</v>
+      </c>
+      <c r="E39">
+        <v>47</v>
+      </c>
+      <c r="F39">
+        <v>67</v>
+      </c>
+      <c r="G39">
+        <v>68</v>
+      </c>
+      <c r="H39">
+        <v>57</v>
+      </c>
+      <c r="I39">
+        <v>35</v>
+      </c>
+      <c r="J39">
+        <v>1</v>
+      </c>
+      <c r="K39">
+        <v>7</v>
+      </c>
+      <c r="L39">
+        <v>87</v>
+      </c>
+      <c r="M39">
+        <v>75</v>
+      </c>
+      <c r="N39">
+        <v>54</v>
+      </c>
+      <c r="O39">
+        <v>37</v>
+      </c>
+      <c r="P39">
+        <v>48</v>
+      </c>
+      <c r="Q39">
+        <v>3</v>
+      </c>
+      <c r="R39">
+        <v>51</v>
+      </c>
+      <c r="S39">
+        <v>86</v>
+      </c>
+      <c r="T39">
+        <v>65</v>
+      </c>
+      <c r="U39">
+        <v>64</v>
+      </c>
+      <c r="V39">
+        <v>42</v>
+      </c>
+      <c r="W39">
+        <v>52</v>
+      </c>
+      <c r="Y39">
+        <v>58</v>
+      </c>
+      <c r="Z39">
+        <v>47</v>
+      </c>
+      <c r="AA39">
+        <v>75</v>
+      </c>
+      <c r="AB39">
+        <v>63</v>
+      </c>
+      <c r="AC39">
+        <v>52</v>
+      </c>
+      <c r="AD39">
+        <v>37</v>
+      </c>
+      <c r="AE39">
+        <v>1</v>
+      </c>
+      <c r="AF39">
+        <v>56</v>
+      </c>
+      <c r="AG39">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="40" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B40" s="1">
+        <v>2</v>
+      </c>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1">
+        <v>1</v>
+      </c>
+      <c r="E40" s="1">
+        <v>2</v>
+      </c>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1">
+        <v>6</v>
+      </c>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1">
+        <v>1</v>
+      </c>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1">
+        <v>6</v>
+      </c>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1">
+        <v>4</v>
+      </c>
+      <c r="O40" s="1"/>
+      <c r="P40" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q40" s="1"/>
+      <c r="R40" s="1"/>
+      <c r="S40" s="1">
+        <v>3</v>
+      </c>
+      <c r="T40" s="1"/>
+      <c r="U40" s="1">
+        <v>8</v>
+      </c>
+      <c r="V40" s="1"/>
+      <c r="W40" s="1"/>
+      <c r="X40" s="1"/>
+      <c r="Y40" s="1"/>
+      <c r="Z40" s="1">
+        <v>4</v>
+      </c>
+      <c r="AA40" s="1"/>
+      <c r="AB40" s="1">
+        <v>2</v>
+      </c>
+      <c r="AC40" s="1"/>
+      <c r="AD40" s="1">
+        <v>2</v>
+      </c>
+      <c r="AE40" s="1"/>
+      <c r="AF40" s="1"/>
+      <c r="AG40" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>50</v>
+      </c>
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="D41">
+        <v>2</v>
+      </c>
+      <c r="E41">
+        <v>3</v>
+      </c>
+      <c r="F41">
+        <v>2</v>
+      </c>
+      <c r="G41">
+        <v>3</v>
+      </c>
+      <c r="K41">
+        <v>5</v>
+      </c>
+      <c r="L41">
+        <v>4</v>
+      </c>
+      <c r="M41">
+        <v>3</v>
+      </c>
+      <c r="O41">
+        <v>1</v>
+      </c>
+      <c r="P41">
+        <v>3</v>
+      </c>
+      <c r="R41">
+        <v>4</v>
+      </c>
+      <c r="S41">
+        <v>3</v>
+      </c>
+      <c r="T41">
+        <v>1</v>
+      </c>
+      <c r="U41">
+        <v>3</v>
+      </c>
+      <c r="V41">
+        <v>1</v>
+      </c>
+      <c r="W41">
+        <v>9</v>
+      </c>
+      <c r="Z41">
+        <v>7</v>
+      </c>
+      <c r="AA41">
+        <v>1</v>
+      </c>
+      <c r="AB41">
+        <v>3</v>
+      </c>
+      <c r="AE41">
+        <v>1</v>
+      </c>
+      <c r="AF41">
+        <v>1</v>
+      </c>
+      <c r="AG41">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1">
+        <v>2</v>
+      </c>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1">
+        <v>41</v>
+      </c>
+      <c r="O42" s="1">
+        <v>55</v>
+      </c>
+      <c r="P42" s="1"/>
+      <c r="Q42" s="1"/>
+      <c r="R42" s="1">
+        <v>16</v>
+      </c>
+      <c r="S42" s="1">
+        <v>30</v>
+      </c>
+      <c r="T42" s="1">
+        <v>28</v>
+      </c>
+      <c r="U42" s="1">
+        <v>14</v>
+      </c>
+      <c r="V42" s="1">
+        <v>21</v>
+      </c>
+      <c r="W42" s="1"/>
+      <c r="X42" s="1"/>
+      <c r="Y42" s="1">
+        <v>19</v>
+      </c>
+      <c r="Z42" s="1">
+        <v>32</v>
+      </c>
+      <c r="AA42" s="1">
+        <v>10</v>
+      </c>
+      <c r="AB42" s="1">
+        <v>20</v>
+      </c>
+      <c r="AC42" s="1">
+        <v>23</v>
+      </c>
+      <c r="AD42" s="1"/>
+      <c r="AE42" s="1"/>
+      <c r="AF42" s="1">
+        <v>21</v>
+      </c>
+      <c r="AG42" s="1">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="43" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>52</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+      <c r="M43">
+        <v>3</v>
+      </c>
+      <c r="N43">
+        <v>48</v>
+      </c>
+      <c r="O43">
+        <v>60</v>
+      </c>
+      <c r="R43">
+        <v>80</v>
+      </c>
+      <c r="S43">
+        <v>77</v>
+      </c>
+      <c r="T43">
+        <v>52</v>
+      </c>
+      <c r="U43">
+        <v>73</v>
+      </c>
+      <c r="V43">
+        <v>66</v>
+      </c>
+      <c r="Y43">
+        <v>85</v>
+      </c>
+      <c r="Z43">
+        <v>80</v>
+      </c>
+      <c r="AA43">
+        <v>53</v>
+      </c>
+      <c r="AB43">
+        <v>57</v>
+      </c>
+      <c r="AC43">
+        <v>60</v>
+      </c>
+      <c r="AF43">
+        <v>88</v>
+      </c>
+      <c r="AG43">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="44" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1">
+        <v>2</v>
+      </c>
+      <c r="O44" s="1">
+        <v>6</v>
+      </c>
+      <c r="P44" s="1"/>
+      <c r="Q44" s="1"/>
+      <c r="R44" s="1">
+        <v>3</v>
+      </c>
+      <c r="S44" s="1">
+        <v>1</v>
+      </c>
+      <c r="T44" s="1">
+        <v>5</v>
+      </c>
+      <c r="U44" s="1"/>
+      <c r="V44" s="1">
+        <v>5</v>
+      </c>
+      <c r="W44" s="1"/>
+      <c r="X44" s="1"/>
+      <c r="Y44" s="1">
+        <v>4</v>
+      </c>
+      <c r="Z44" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA44" s="1">
+        <v>4</v>
+      </c>
+      <c r="AB44" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC44" s="1"/>
+      <c r="AD44" s="1"/>
+      <c r="AE44" s="1"/>
+      <c r="AF44" s="1">
+        <v>2</v>
+      </c>
+      <c r="AG44" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>54</v>
+      </c>
+      <c r="O45">
+        <v>165</v>
+      </c>
+      <c r="R45">
+        <v>12</v>
+      </c>
+      <c r="S45">
+        <v>6</v>
+      </c>
+      <c r="T45">
+        <v>6</v>
+      </c>
+      <c r="U45">
+        <v>11</v>
+      </c>
+      <c r="V45">
+        <v>22</v>
+      </c>
+      <c r="Y45">
+        <v>16</v>
+      </c>
+      <c r="Z45">
+        <v>8</v>
+      </c>
+      <c r="AA45">
+        <v>10</v>
+      </c>
+      <c r="AB45">
+        <v>5</v>
+      </c>
+      <c r="AC45">
+        <v>3</v>
+      </c>
+      <c r="AF45">
+        <v>7</v>
+      </c>
+      <c r="AG45">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="46" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B46" s="1">
+        <v>3</v>
+      </c>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1">
+        <v>6</v>
+      </c>
+      <c r="E46" s="1">
+        <v>2</v>
+      </c>
+      <c r="F46" s="1">
+        <v>6</v>
+      </c>
+      <c r="G46" s="1">
+        <v>10</v>
+      </c>
+      <c r="H46" s="1">
+        <v>2</v>
+      </c>
+      <c r="I46" s="1">
+        <v>1</v>
+      </c>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+      <c r="N46" s="1"/>
+      <c r="O46" s="1">
+        <v>1</v>
+      </c>
+      <c r="P46" s="1"/>
+      <c r="Q46" s="1"/>
+      <c r="R46" s="1">
+        <v>5</v>
+      </c>
+      <c r="S46" s="1"/>
+      <c r="T46" s="1">
+        <v>13</v>
+      </c>
+      <c r="U46" s="1">
+        <v>5</v>
+      </c>
+      <c r="V46" s="1">
+        <v>2</v>
+      </c>
+      <c r="W46" s="1">
+        <v>1</v>
+      </c>
+      <c r="X46" s="1">
+        <v>3</v>
+      </c>
+      <c r="Y46" s="1">
+        <v>7</v>
+      </c>
+      <c r="Z46" s="1">
+        <v>5</v>
+      </c>
+      <c r="AA46" s="1">
+        <v>8</v>
+      </c>
+      <c r="AB46" s="1">
+        <v>3</v>
+      </c>
+      <c r="AC46" s="1">
+        <v>8</v>
+      </c>
+      <c r="AD46" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE46" s="1"/>
+      <c r="AF46" s="1">
+        <v>3</v>
+      </c>
+      <c r="AG46" s="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="47" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>56</v>
+      </c>
+      <c r="B47">
+        <v>3</v>
+      </c>
+      <c r="D47">
+        <v>19</v>
+      </c>
+      <c r="E47">
+        <v>25</v>
+      </c>
+      <c r="F47">
+        <v>10</v>
+      </c>
+      <c r="G47">
+        <v>22</v>
+      </c>
+      <c r="H47">
+        <v>5</v>
+      </c>
+      <c r="I47">
+        <v>3</v>
+      </c>
+      <c r="K47">
+        <v>23</v>
+      </c>
+      <c r="L47">
+        <v>29</v>
+      </c>
+      <c r="M47">
+        <v>18</v>
+      </c>
+      <c r="N47">
+        <v>25</v>
+      </c>
+      <c r="O47">
+        <v>14</v>
+      </c>
+      <c r="P47">
+        <v>7</v>
+      </c>
+      <c r="Q47">
+        <v>1</v>
+      </c>
+      <c r="R47">
+        <v>16</v>
+      </c>
+      <c r="S47">
+        <v>26</v>
+      </c>
+      <c r="T47">
+        <v>30</v>
+      </c>
+      <c r="U47">
+        <v>17</v>
+      </c>
+      <c r="V47">
+        <v>28</v>
+      </c>
+      <c r="W47">
+        <v>5</v>
+      </c>
+      <c r="X47">
+        <v>1</v>
+      </c>
+      <c r="Y47">
+        <v>18</v>
+      </c>
+      <c r="Z47">
+        <v>34</v>
+      </c>
+      <c r="AA47">
+        <v>54</v>
+      </c>
+      <c r="AB47">
+        <v>21</v>
+      </c>
+      <c r="AC47">
+        <v>9</v>
+      </c>
+      <c r="AD47">
+        <v>6</v>
+      </c>
+      <c r="AE47">
+        <v>1</v>
+      </c>
+      <c r="AF47">
+        <v>17</v>
+      </c>
+      <c r="AG47">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="48" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B48" s="1">
+        <v>20</v>
+      </c>
+      <c r="C48" s="1">
+        <v>1</v>
+      </c>
+      <c r="D48" s="1">
+        <v>27</v>
+      </c>
+      <c r="E48" s="1">
+        <v>23</v>
+      </c>
+      <c r="F48" s="1">
+        <v>38</v>
+      </c>
+      <c r="G48" s="1">
+        <v>28</v>
+      </c>
+      <c r="H48" s="1">
+        <v>30</v>
+      </c>
+      <c r="I48" s="1">
+        <v>11</v>
+      </c>
+      <c r="J48" s="1"/>
+      <c r="K48" s="1">
+        <v>32</v>
+      </c>
+      <c r="L48" s="1">
+        <v>15</v>
+      </c>
+      <c r="M48" s="1">
+        <v>44</v>
+      </c>
+      <c r="N48" s="1">
+        <v>18</v>
+      </c>
+      <c r="O48" s="1">
+        <v>21</v>
+      </c>
+      <c r="P48" s="1">
+        <v>14</v>
+      </c>
+      <c r="Q48" s="1">
+        <v>2</v>
+      </c>
+      <c r="R48" s="1">
+        <v>26</v>
+      </c>
+      <c r="S48" s="1">
+        <v>25</v>
+      </c>
+      <c r="T48" s="1">
+        <v>36</v>
+      </c>
+      <c r="U48" s="1">
+        <v>22</v>
+      </c>
+      <c r="V48" s="1">
+        <v>26</v>
+      </c>
+      <c r="W48" s="1">
+        <v>18</v>
+      </c>
+      <c r="X48" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y48" s="1">
+        <v>29</v>
+      </c>
+      <c r="Z48" s="1">
+        <v>42</v>
+      </c>
+      <c r="AA48" s="1">
+        <v>28</v>
+      </c>
+      <c r="AB48" s="1">
+        <v>15</v>
+      </c>
+      <c r="AC48" s="1">
+        <v>29</v>
+      </c>
+      <c r="AD48" s="1">
+        <v>22</v>
+      </c>
+      <c r="AE48" s="1"/>
+      <c r="AF48" s="1">
+        <v>31</v>
+      </c>
+      <c r="AG48" s="1">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="49" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>58</v>
+      </c>
+      <c r="B49">
+        <v>9</v>
+      </c>
+      <c r="D49">
+        <v>27</v>
+      </c>
+      <c r="E49">
+        <v>25</v>
+      </c>
+      <c r="F49">
+        <v>13</v>
+      </c>
+      <c r="G49">
+        <v>16</v>
+      </c>
+      <c r="H49">
+        <v>20</v>
+      </c>
+      <c r="I49">
+        <v>9</v>
+      </c>
+      <c r="K49">
+        <v>21</v>
+      </c>
+      <c r="L49">
+        <v>20</v>
+      </c>
+      <c r="M49">
+        <v>31</v>
+      </c>
+      <c r="N49">
+        <v>14</v>
+      </c>
+      <c r="O49">
+        <v>21</v>
+      </c>
+      <c r="P49">
+        <v>10</v>
+      </c>
+      <c r="R49">
+        <v>31</v>
+      </c>
+      <c r="S49">
+        <v>24</v>
+      </c>
+      <c r="T49">
+        <v>13</v>
+      </c>
+      <c r="U49">
+        <v>16</v>
+      </c>
+      <c r="V49">
+        <v>19</v>
+      </c>
+      <c r="W49">
+        <v>9</v>
+      </c>
+      <c r="X49">
+        <v>1</v>
+      </c>
+      <c r="Y49">
+        <v>17</v>
+      </c>
+      <c r="Z49">
+        <v>22</v>
+      </c>
+      <c r="AA49">
+        <v>16</v>
+      </c>
+      <c r="AB49">
+        <v>20</v>
+      </c>
+      <c r="AC49">
+        <v>18</v>
+      </c>
+      <c r="AD49">
+        <v>6</v>
+      </c>
+      <c r="AE49">
+        <v>1</v>
+      </c>
+      <c r="AF49">
+        <v>37</v>
+      </c>
+      <c r="AG49">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="50" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B50" s="1">
+        <v>3</v>
+      </c>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1">
+        <v>7</v>
+      </c>
+      <c r="E50" s="1">
+        <v>9</v>
+      </c>
+      <c r="F50" s="1">
+        <v>39</v>
+      </c>
+      <c r="G50" s="1">
+        <v>6</v>
+      </c>
+      <c r="H50" s="1">
+        <v>17</v>
+      </c>
+      <c r="I50" s="1">
+        <v>8</v>
+      </c>
+      <c r="J50" s="1">
+        <v>1</v>
+      </c>
+      <c r="K50" s="1">
+        <v>9</v>
+      </c>
+      <c r="L50" s="1">
+        <v>23</v>
+      </c>
+      <c r="M50" s="1">
+        <v>26</v>
+      </c>
+      <c r="N50" s="1">
+        <v>19</v>
+      </c>
+      <c r="O50" s="1">
+        <v>22</v>
+      </c>
+      <c r="P50" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q50" s="1">
+        <v>2</v>
+      </c>
+      <c r="R50" s="1">
+        <v>16</v>
+      </c>
+      <c r="S50" s="1">
+        <v>18</v>
+      </c>
+      <c r="T50" s="1">
+        <v>19</v>
+      </c>
+      <c r="U50" s="1">
+        <v>10</v>
+      </c>
+      <c r="V50" s="1">
+        <v>17</v>
+      </c>
+      <c r="W50" s="1">
+        <v>6</v>
+      </c>
+      <c r="X50" s="1"/>
+      <c r="Y50" s="1">
+        <v>13</v>
+      </c>
+      <c r="Z50" s="1">
+        <v>14</v>
+      </c>
+      <c r="AA50" s="1">
+        <v>18</v>
+      </c>
+      <c r="AB50" s="1">
+        <v>10</v>
+      </c>
+      <c r="AC50" s="1">
+        <v>19</v>
+      </c>
+      <c r="AD50" s="1">
+        <v>2</v>
+      </c>
+      <c r="AE50" s="1">
+        <v>1</v>
+      </c>
+      <c r="AF50" s="1">
+        <v>16</v>
+      </c>
+      <c r="AG50" s="1">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="51" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B51">
+        <v>20</v>
+      </c>
+      <c r="C51">
+        <v>18</v>
+      </c>
+      <c r="D51">
+        <v>38</v>
+      </c>
+      <c r="E51">
+        <v>64</v>
+      </c>
+      <c r="F51">
+        <v>36</v>
+      </c>
+      <c r="G51">
+        <v>49</v>
+      </c>
+      <c r="H51">
+        <v>55</v>
+      </c>
+      <c r="I51">
+        <v>32</v>
+      </c>
+      <c r="J51">
+        <v>12</v>
+      </c>
+      <c r="K51">
+        <v>47</v>
+      </c>
+      <c r="L51">
+        <v>54</v>
+      </c>
+      <c r="M51">
+        <v>55</v>
+      </c>
+      <c r="N51">
+        <v>62</v>
+      </c>
+      <c r="O51">
+        <v>49</v>
+      </c>
+      <c r="P51">
+        <v>34</v>
+      </c>
+      <c r="Q51">
+        <v>26</v>
+      </c>
+      <c r="R51">
+        <v>62</v>
+      </c>
+      <c r="S51">
+        <v>62</v>
+      </c>
+      <c r="T51">
+        <v>49</v>
+      </c>
+      <c r="U51">
+        <v>57</v>
+      </c>
+      <c r="V51">
+        <v>44</v>
+      </c>
+      <c r="W51">
+        <v>25</v>
+      </c>
+      <c r="X51">
+        <v>18</v>
+      </c>
+      <c r="Y51">
+        <v>52</v>
+      </c>
+      <c r="Z51">
+        <v>47</v>
+      </c>
+      <c r="AA51">
+        <v>51</v>
+      </c>
+      <c r="AB51">
+        <v>76</v>
+      </c>
+      <c r="AC51">
+        <v>57</v>
+      </c>
+      <c r="AD51">
+        <v>23</v>
+      </c>
+      <c r="AE51">
+        <v>20</v>
+      </c>
+      <c r="AF51">
+        <v>41</v>
+      </c>
+      <c r="AG51">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="52" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1">
+        <v>7</v>
+      </c>
+      <c r="E52" s="1">
+        <v>10</v>
+      </c>
+      <c r="F52" s="1">
+        <v>7</v>
+      </c>
+      <c r="G52" s="1">
+        <v>7</v>
+      </c>
+      <c r="H52" s="1">
+        <v>4</v>
+      </c>
+      <c r="I52" s="1">
+        <v>3</v>
+      </c>
+      <c r="J52" s="1"/>
+      <c r="K52" s="1">
+        <v>7</v>
+      </c>
+      <c r="L52" s="1">
+        <v>5</v>
+      </c>
+      <c r="M52" s="1">
+        <v>7</v>
+      </c>
+      <c r="N52" s="1">
+        <v>4</v>
+      </c>
+      <c r="O52" s="1">
+        <v>6</v>
+      </c>
+      <c r="P52" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="1">
+        <v>1</v>
+      </c>
+      <c r="R52" s="1">
+        <v>4</v>
+      </c>
+      <c r="S52" s="1">
+        <v>6</v>
+      </c>
+      <c r="T52" s="1">
+        <v>10</v>
+      </c>
+      <c r="U52" s="1">
+        <v>3</v>
+      </c>
+      <c r="V52" s="1">
+        <v>4</v>
+      </c>
+      <c r="W52" s="1">
+        <v>2</v>
+      </c>
+      <c r="X52" s="1"/>
+      <c r="Y52" s="1">
+        <v>7</v>
+      </c>
+      <c r="Z52" s="1">
+        <v>3</v>
+      </c>
+      <c r="AA52" s="1">
+        <v>8</v>
+      </c>
+      <c r="AB52" s="1">
+        <v>6</v>
+      </c>
+      <c r="AC52" s="1">
+        <v>9</v>
+      </c>
+      <c r="AD52" s="1">
+        <v>6</v>
+      </c>
+      <c r="AE52" s="1"/>
+      <c r="AF52" s="1">
+        <v>4</v>
+      </c>
+      <c r="AG52" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="53" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>62</v>
+      </c>
+      <c r="B53">
+        <v>4</v>
+      </c>
+      <c r="D53">
+        <v>11</v>
+      </c>
+      <c r="E53">
+        <v>15</v>
+      </c>
+      <c r="F53">
+        <v>15</v>
+      </c>
+      <c r="G53">
+        <v>6</v>
+      </c>
+      <c r="H53">
+        <v>11</v>
+      </c>
+      <c r="I53">
+        <v>6</v>
+      </c>
+      <c r="K53">
+        <v>15</v>
+      </c>
+      <c r="L53">
+        <v>10</v>
+      </c>
+      <c r="M53">
+        <v>10</v>
+      </c>
+      <c r="N53">
+        <v>12</v>
+      </c>
+      <c r="O53">
+        <v>9</v>
+      </c>
+      <c r="P53">
+        <v>7</v>
+      </c>
+      <c r="R53">
+        <v>15</v>
+      </c>
+      <c r="S53">
+        <v>9</v>
+      </c>
+      <c r="T53">
+        <v>19</v>
+      </c>
+      <c r="U53">
+        <v>8</v>
+      </c>
+      <c r="V53">
+        <v>10</v>
+      </c>
+      <c r="W53">
+        <v>4</v>
+      </c>
+      <c r="Y53">
+        <v>17</v>
+      </c>
+      <c r="Z53">
+        <v>11</v>
+      </c>
+      <c r="AA53">
+        <v>10</v>
+      </c>
+      <c r="AB53">
+        <v>9</v>
+      </c>
+      <c r="AC53">
+        <v>15</v>
+      </c>
+      <c r="AD53">
+        <v>4</v>
+      </c>
+      <c r="AF53">
+        <v>11</v>
+      </c>
+      <c r="AG53">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="54" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B54" s="1">
+        <v>2</v>
+      </c>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1">
+        <v>4</v>
+      </c>
+      <c r="E54" s="1">
+        <v>2</v>
+      </c>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1">
+        <v>2</v>
+      </c>
+      <c r="H54" s="1">
+        <v>3</v>
+      </c>
+      <c r="I54" s="1">
+        <v>2</v>
+      </c>
+      <c r="J54" s="1"/>
+      <c r="K54" s="1">
+        <v>3</v>
+      </c>
+      <c r="L54" s="1"/>
+      <c r="M54" s="1">
+        <v>3</v>
+      </c>
+      <c r="N54" s="1">
+        <v>3</v>
+      </c>
+      <c r="O54" s="1">
+        <v>3</v>
+      </c>
+      <c r="P54" s="1"/>
+      <c r="Q54" s="1"/>
+      <c r="R54" s="1">
+        <v>1</v>
+      </c>
+      <c r="S54" s="1">
+        <v>2</v>
+      </c>
+      <c r="T54" s="1">
+        <v>3</v>
+      </c>
+      <c r="U54" s="1">
+        <v>1</v>
+      </c>
+      <c r="V54" s="1">
+        <v>5</v>
+      </c>
+      <c r="W54" s="1">
+        <v>3</v>
+      </c>
+      <c r="X54" s="1"/>
+      <c r="Y54" s="1">
+        <v>2</v>
+      </c>
+      <c r="Z54" s="1">
+        <v>3</v>
+      </c>
+      <c r="AA54" s="1">
+        <v>3</v>
+      </c>
+      <c r="AB54" s="1">
+        <v>2</v>
+      </c>
+      <c r="AC54" s="1">
+        <v>3</v>
+      </c>
+      <c r="AD54" s="1"/>
+      <c r="AE54" s="1"/>
+      <c r="AF54" s="1">
+        <v>3</v>
+      </c>
+      <c r="AG54" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="55" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>64</v>
+      </c>
+      <c r="B55">
+        <v>3</v>
+      </c>
+      <c r="D55">
+        <v>1</v>
+      </c>
+      <c r="E55">
+        <v>4</v>
+      </c>
+      <c r="F55">
+        <v>6</v>
+      </c>
+      <c r="K55">
+        <v>1</v>
+      </c>
+      <c r="L55">
+        <v>7</v>
+      </c>
+      <c r="M55">
+        <v>5</v>
+      </c>
+      <c r="N55">
+        <v>1</v>
+      </c>
+      <c r="P55">
+        <v>3</v>
+      </c>
+      <c r="R55">
+        <v>4</v>
+      </c>
+      <c r="S55">
+        <v>1</v>
+      </c>
+      <c r="T55">
+        <v>5</v>
+      </c>
+      <c r="U55">
+        <v>4</v>
+      </c>
+      <c r="W55">
+        <v>2</v>
+      </c>
+      <c r="Y55">
+        <v>4</v>
+      </c>
+      <c r="Z55">
+        <v>4</v>
+      </c>
+      <c r="AA55">
+        <v>5</v>
+      </c>
+      <c r="AB55">
+        <v>1</v>
+      </c>
+      <c r="AC55">
+        <v>1</v>
+      </c>
+      <c r="AD55">
+        <v>1</v>
+      </c>
+      <c r="AG55">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="56" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B56" s="1">
+        <v>2</v>
+      </c>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1">
+        <v>12</v>
+      </c>
+      <c r="E56" s="1">
+        <v>2</v>
+      </c>
+      <c r="F56" s="1">
+        <v>6</v>
+      </c>
+      <c r="G56" s="1">
+        <v>8</v>
+      </c>
+      <c r="H56" s="1">
+        <v>10</v>
+      </c>
+      <c r="I56" s="1">
+        <v>1</v>
+      </c>
+      <c r="J56" s="1"/>
+      <c r="K56" s="1">
+        <v>9</v>
+      </c>
+      <c r="L56" s="1">
+        <v>4</v>
+      </c>
+      <c r="M56" s="1">
+        <v>3</v>
+      </c>
+      <c r="N56" s="1">
+        <v>7</v>
+      </c>
+      <c r="O56" s="1">
+        <v>8</v>
+      </c>
+      <c r="P56" s="1"/>
+      <c r="Q56" s="1">
+        <v>1</v>
+      </c>
+      <c r="R56" s="1">
+        <v>10</v>
+      </c>
+      <c r="S56" s="1">
+        <v>2</v>
+      </c>
+      <c r="T56" s="1">
+        <v>5</v>
+      </c>
+      <c r="U56" s="1">
+        <v>12</v>
+      </c>
+      <c r="V56" s="1">
+        <v>6</v>
+      </c>
+      <c r="W56" s="1">
+        <v>2</v>
+      </c>
+      <c r="X56" s="1"/>
+      <c r="Y56" s="1">
+        <v>6</v>
+      </c>
+      <c r="Z56" s="1">
+        <v>7</v>
+      </c>
+      <c r="AA56" s="1">
+        <v>8</v>
+      </c>
+      <c r="AB56" s="1">
+        <v>11</v>
+      </c>
+      <c r="AC56" s="1">
+        <v>4</v>
+      </c>
+      <c r="AD56" s="1"/>
+      <c r="AE56" s="1"/>
+      <c r="AF56" s="1">
+        <v>6</v>
+      </c>
+      <c r="AG56" s="1">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:AG3" xr:uid="{00000000-0001-0000-0700-000000000000}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:AG56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -38223,1293 +42901,7 @@
       <c r="AG56" s="1"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:AG56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="2" max="32" width="12.7109375" customWidth="1"/>
-    <col min="33" max="33" width="15.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:33" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2">
-        <v>9</v>
-      </c>
-      <c r="K1" s="2">
-        <v>10</v>
-      </c>
-      <c r="L1" s="2">
-        <v>11</v>
-      </c>
-      <c r="M1" s="2">
-        <v>12</v>
-      </c>
-      <c r="N1" s="2">
-        <v>13</v>
-      </c>
-      <c r="O1" s="2">
-        <v>14</v>
-      </c>
-      <c r="P1" s="2">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="2">
-        <v>16</v>
-      </c>
-      <c r="R1" s="2">
-        <v>17</v>
-      </c>
-      <c r="S1" s="2">
-        <v>18</v>
-      </c>
-      <c r="T1" s="2">
-        <v>19</v>
-      </c>
-      <c r="U1" s="2">
-        <v>20</v>
-      </c>
-      <c r="V1" s="2">
-        <v>21</v>
-      </c>
-      <c r="W1" s="2">
-        <v>22</v>
-      </c>
-      <c r="X1" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y1" s="2">
-        <v>24</v>
-      </c>
-      <c r="Z1" s="2">
-        <v>25</v>
-      </c>
-      <c r="AA1" s="2">
-        <v>26</v>
-      </c>
-      <c r="AB1" s="2">
-        <v>27</v>
-      </c>
-      <c r="AC1" s="2">
-        <v>28</v>
-      </c>
-      <c r="AD1" s="2">
-        <v>29</v>
-      </c>
-      <c r="AE1" s="2">
-        <v>30</v>
-      </c>
-      <c r="AF1" s="2">
-        <v>31</v>
-      </c>
-      <c r="AG1" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:33" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-      <c r="U2" s="3"/>
-      <c r="V2" s="3"/>
-      <c r="W2" s="3"/>
-      <c r="X2" s="3"/>
-      <c r="Y2" s="3"/>
-      <c r="Z2" s="3"/>
-      <c r="AA2" s="3"/>
-      <c r="AB2" s="3"/>
-      <c r="AC2" s="3"/>
-      <c r="AD2" s="3"/>
-      <c r="AE2" s="3"/>
-      <c r="AF2" s="3"/>
-    </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
-      <c r="R4" s="1"/>
-      <c r="S4" s="1"/>
-      <c r="T4" s="1"/>
-      <c r="U4" s="1"/>
-      <c r="V4" s="1"/>
-      <c r="W4" s="1"/>
-      <c r="X4" s="1"/>
-      <c r="Y4" s="1"/>
-      <c r="Z4" s="1"/>
-      <c r="AA4" s="1"/>
-      <c r="AB4" s="1"/>
-      <c r="AC4" s="1"/>
-      <c r="AD4" s="1"/>
-      <c r="AE4" s="1"/>
-      <c r="AF4" s="1"/>
-      <c r="AG4" s="1"/>
-    </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
-      <c r="R6" s="1"/>
-      <c r="S6" s="1"/>
-      <c r="T6" s="1"/>
-      <c r="U6" s="1"/>
-      <c r="V6" s="1"/>
-      <c r="W6" s="1"/>
-      <c r="X6" s="1"/>
-      <c r="Y6" s="1"/>
-      <c r="Z6" s="1"/>
-      <c r="AA6" s="1"/>
-      <c r="AB6" s="1"/>
-      <c r="AC6" s="1"/>
-      <c r="AD6" s="1"/>
-      <c r="AE6" s="1"/>
-      <c r="AF6" s="1"/>
-      <c r="AG6" s="1"/>
-    </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="1"/>
-      <c r="T8" s="1"/>
-      <c r="U8" s="1"/>
-      <c r="V8" s="1"/>
-      <c r="W8" s="1"/>
-      <c r="X8" s="1"/>
-      <c r="Y8" s="1"/>
-      <c r="Z8" s="1"/>
-      <c r="AA8" s="1"/>
-      <c r="AB8" s="1"/>
-      <c r="AC8" s="1"/>
-      <c r="AD8" s="1"/>
-      <c r="AE8" s="1"/>
-      <c r="AF8" s="1"/>
-      <c r="AG8" s="1"/>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
-      <c r="Q10" s="1"/>
-      <c r="R10" s="1"/>
-      <c r="S10" s="1"/>
-      <c r="T10" s="1"/>
-      <c r="U10" s="1"/>
-      <c r="V10" s="1"/>
-      <c r="W10" s="1"/>
-      <c r="X10" s="1"/>
-      <c r="Y10" s="1"/>
-      <c r="Z10" s="1"/>
-      <c r="AA10" s="1"/>
-      <c r="AB10" s="1"/>
-      <c r="AC10" s="1"/>
-      <c r="AD10" s="1"/>
-      <c r="AE10" s="1"/>
-      <c r="AF10" s="1"/>
-      <c r="AG10" s="1"/>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
-      <c r="Q12" s="1"/>
-      <c r="R12" s="1"/>
-      <c r="S12" s="1"/>
-      <c r="T12" s="1"/>
-      <c r="U12" s="1"/>
-      <c r="V12" s="1"/>
-      <c r="W12" s="1"/>
-      <c r="X12" s="1"/>
-      <c r="Y12" s="1"/>
-      <c r="Z12" s="1"/>
-      <c r="AA12" s="1"/>
-      <c r="AB12" s="1"/>
-      <c r="AC12" s="1"/>
-      <c r="AD12" s="1"/>
-      <c r="AE12" s="1"/>
-      <c r="AF12" s="1"/>
-      <c r="AG12" s="1"/>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-      <c r="P14" s="1"/>
-      <c r="Q14" s="1"/>
-      <c r="R14" s="1"/>
-      <c r="S14" s="1"/>
-      <c r="T14" s="1"/>
-      <c r="U14" s="1"/>
-      <c r="V14" s="1"/>
-      <c r="W14" s="1"/>
-      <c r="X14" s="1"/>
-      <c r="Y14" s="1"/>
-      <c r="Z14" s="1"/>
-      <c r="AA14" s="1"/>
-      <c r="AB14" s="1"/>
-      <c r="AC14" s="1"/>
-      <c r="AD14" s="1"/>
-      <c r="AE14" s="1"/>
-      <c r="AF14" s="1"/>
-      <c r="AG14" s="1"/>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1"/>
-      <c r="S16" s="1"/>
-      <c r="T16" s="1"/>
-      <c r="U16" s="1"/>
-      <c r="V16" s="1"/>
-      <c r="W16" s="1"/>
-      <c r="X16" s="1"/>
-      <c r="Y16" s="1"/>
-      <c r="Z16" s="1"/>
-      <c r="AA16" s="1"/>
-      <c r="AB16" s="1"/>
-      <c r="AC16" s="1"/>
-      <c r="AD16" s="1"/>
-      <c r="AE16" s="1"/>
-      <c r="AF16" s="1"/>
-      <c r="AG16" s="1"/>
-    </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
-      <c r="P18" s="1"/>
-      <c r="Q18" s="1"/>
-      <c r="R18" s="1"/>
-      <c r="S18" s="1"/>
-      <c r="T18" s="1"/>
-      <c r="U18" s="1"/>
-      <c r="V18" s="1"/>
-      <c r="W18" s="1"/>
-      <c r="X18" s="1"/>
-      <c r="Y18" s="1"/>
-      <c r="Z18" s="1"/>
-      <c r="AA18" s="1"/>
-      <c r="AB18" s="1"/>
-      <c r="AC18" s="1"/>
-      <c r="AD18" s="1"/>
-      <c r="AE18" s="1"/>
-      <c r="AF18" s="1"/>
-      <c r="AG18" s="1"/>
-    </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-      <c r="P20" s="1"/>
-      <c r="Q20" s="1"/>
-      <c r="R20" s="1"/>
-      <c r="S20" s="1"/>
-      <c r="T20" s="1"/>
-      <c r="U20" s="1"/>
-      <c r="V20" s="1"/>
-      <c r="W20" s="1"/>
-      <c r="X20" s="1"/>
-      <c r="Y20" s="1"/>
-      <c r="Z20" s="1"/>
-      <c r="AA20" s="1"/>
-      <c r="AB20" s="1"/>
-      <c r="AC20" s="1"/>
-      <c r="AD20" s="1"/>
-      <c r="AE20" s="1"/>
-      <c r="AF20" s="1"/>
-      <c r="AG20" s="1"/>
-    </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1"/>
-      <c r="Q22" s="1"/>
-      <c r="R22" s="1"/>
-      <c r="S22" s="1"/>
-      <c r="T22" s="1"/>
-      <c r="U22" s="1"/>
-      <c r="V22" s="1"/>
-      <c r="W22" s="1"/>
-      <c r="X22" s="1"/>
-      <c r="Y22" s="1"/>
-      <c r="Z22" s="1"/>
-      <c r="AA22" s="1"/>
-      <c r="AB22" s="1"/>
-      <c r="AC22" s="1"/>
-      <c r="AD22" s="1"/>
-      <c r="AE22" s="1"/>
-      <c r="AF22" s="1"/>
-      <c r="AG22" s="1"/>
-    </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1"/>
-      <c r="Q24" s="1"/>
-      <c r="R24" s="1"/>
-      <c r="S24" s="1"/>
-      <c r="T24" s="1"/>
-      <c r="U24" s="1"/>
-      <c r="V24" s="1"/>
-      <c r="W24" s="1"/>
-      <c r="X24" s="1"/>
-      <c r="Y24" s="1"/>
-      <c r="Z24" s="1"/>
-      <c r="AA24" s="1"/>
-      <c r="AB24" s="1"/>
-      <c r="AC24" s="1"/>
-      <c r="AD24" s="1"/>
-      <c r="AE24" s="1"/>
-      <c r="AF24" s="1"/>
-      <c r="AG24" s="1"/>
-    </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
-      <c r="P26" s="1"/>
-      <c r="Q26" s="1"/>
-      <c r="R26" s="1"/>
-      <c r="S26" s="1"/>
-      <c r="T26" s="1"/>
-      <c r="U26" s="1"/>
-      <c r="V26" s="1"/>
-      <c r="W26" s="1"/>
-      <c r="X26" s="1"/>
-      <c r="Y26" s="1"/>
-      <c r="Z26" s="1"/>
-      <c r="AA26" s="1"/>
-      <c r="AB26" s="1"/>
-      <c r="AC26" s="1"/>
-      <c r="AD26" s="1"/>
-      <c r="AE26" s="1"/>
-      <c r="AF26" s="1"/>
-      <c r="AG26" s="1"/>
-    </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-      <c r="P28" s="1"/>
-      <c r="Q28" s="1"/>
-      <c r="R28" s="1"/>
-      <c r="S28" s="1"/>
-      <c r="T28" s="1"/>
-      <c r="U28" s="1"/>
-      <c r="V28" s="1"/>
-      <c r="W28" s="1"/>
-      <c r="X28" s="1"/>
-      <c r="Y28" s="1"/>
-      <c r="Z28" s="1"/>
-      <c r="AA28" s="1"/>
-      <c r="AB28" s="1"/>
-      <c r="AC28" s="1"/>
-      <c r="AD28" s="1"/>
-      <c r="AE28" s="1"/>
-      <c r="AF28" s="1"/>
-      <c r="AG28" s="1"/>
-    </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1"/>
-      <c r="Q30" s="1"/>
-      <c r="R30" s="1"/>
-      <c r="S30" s="1"/>
-      <c r="T30" s="1"/>
-      <c r="U30" s="1"/>
-      <c r="V30" s="1"/>
-      <c r="W30" s="1"/>
-      <c r="X30" s="1"/>
-      <c r="Y30" s="1"/>
-      <c r="Z30" s="1"/>
-      <c r="AA30" s="1"/>
-      <c r="AB30" s="1"/>
-      <c r="AC30" s="1"/>
-      <c r="AD30" s="1"/>
-      <c r="AE30" s="1"/>
-      <c r="AF30" s="1"/>
-      <c r="AG30" s="1"/>
-    </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
-      <c r="P32" s="1"/>
-      <c r="Q32" s="1"/>
-      <c r="R32" s="1"/>
-      <c r="S32" s="1"/>
-      <c r="T32" s="1"/>
-      <c r="U32" s="1"/>
-      <c r="V32" s="1"/>
-      <c r="W32" s="1"/>
-      <c r="X32" s="1"/>
-      <c r="Y32" s="1"/>
-      <c r="Z32" s="1"/>
-      <c r="AA32" s="1"/>
-      <c r="AB32" s="1"/>
-      <c r="AC32" s="1"/>
-      <c r="AD32" s="1"/>
-      <c r="AE32" s="1"/>
-      <c r="AF32" s="1"/>
-      <c r="AG32" s="1"/>
-    </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
-      <c r="P34" s="1"/>
-      <c r="Q34" s="1"/>
-      <c r="R34" s="1"/>
-      <c r="S34" s="1"/>
-      <c r="T34" s="1"/>
-      <c r="U34" s="1"/>
-      <c r="V34" s="1"/>
-      <c r="W34" s="1"/>
-      <c r="X34" s="1"/>
-      <c r="Y34" s="1"/>
-      <c r="Z34" s="1"/>
-      <c r="AA34" s="1"/>
-      <c r="AB34" s="1"/>
-      <c r="AC34" s="1"/>
-      <c r="AD34" s="1"/>
-      <c r="AE34" s="1"/>
-      <c r="AF34" s="1"/>
-      <c r="AG34" s="1"/>
-    </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
-      <c r="M36" s="1"/>
-      <c r="N36" s="1"/>
-      <c r="O36" s="1"/>
-      <c r="P36" s="1"/>
-      <c r="Q36" s="1"/>
-      <c r="R36" s="1"/>
-      <c r="S36" s="1"/>
-      <c r="T36" s="1"/>
-      <c r="U36" s="1"/>
-      <c r="V36" s="1"/>
-      <c r="W36" s="1"/>
-      <c r="X36" s="1"/>
-      <c r="Y36" s="1"/>
-      <c r="Z36" s="1"/>
-      <c r="AA36" s="1"/>
-      <c r="AB36" s="1"/>
-      <c r="AC36" s="1"/>
-      <c r="AD36" s="1"/>
-      <c r="AE36" s="1"/>
-      <c r="AF36" s="1"/>
-      <c r="AG36" s="1"/>
-    </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
-      <c r="M38" s="1"/>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
-      <c r="P38" s="1"/>
-      <c r="Q38" s="1"/>
-      <c r="R38" s="1"/>
-      <c r="S38" s="1"/>
-      <c r="T38" s="1"/>
-      <c r="U38" s="1"/>
-      <c r="V38" s="1"/>
-      <c r="W38" s="1"/>
-      <c r="X38" s="1"/>
-      <c r="Y38" s="1"/>
-      <c r="Z38" s="1"/>
-      <c r="AA38" s="1"/>
-      <c r="AB38" s="1"/>
-      <c r="AC38" s="1"/>
-      <c r="AD38" s="1"/>
-      <c r="AE38" s="1"/>
-      <c r="AF38" s="1"/>
-      <c r="AG38" s="1"/>
-    </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
-      <c r="M40" s="1"/>
-      <c r="N40" s="1"/>
-      <c r="O40" s="1"/>
-      <c r="P40" s="1"/>
-      <c r="Q40" s="1"/>
-      <c r="R40" s="1"/>
-      <c r="S40" s="1"/>
-      <c r="T40" s="1"/>
-      <c r="U40" s="1"/>
-      <c r="V40" s="1"/>
-      <c r="W40" s="1"/>
-      <c r="X40" s="1"/>
-      <c r="Y40" s="1"/>
-      <c r="Z40" s="1"/>
-      <c r="AA40" s="1"/>
-      <c r="AB40" s="1"/>
-      <c r="AC40" s="1"/>
-      <c r="AD40" s="1"/>
-      <c r="AE40" s="1"/>
-      <c r="AF40" s="1"/>
-      <c r="AG40" s="1"/>
-    </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
-      <c r="M42" s="1"/>
-      <c r="N42" s="1"/>
-      <c r="O42" s="1"/>
-      <c r="P42" s="1"/>
-      <c r="Q42" s="1"/>
-      <c r="R42" s="1"/>
-      <c r="S42" s="1"/>
-      <c r="T42" s="1"/>
-      <c r="U42" s="1"/>
-      <c r="V42" s="1"/>
-      <c r="W42" s="1"/>
-      <c r="X42" s="1"/>
-      <c r="Y42" s="1"/>
-      <c r="Z42" s="1"/>
-      <c r="AA42" s="1"/>
-      <c r="AB42" s="1"/>
-      <c r="AC42" s="1"/>
-      <c r="AD42" s="1"/>
-      <c r="AE42" s="1"/>
-      <c r="AF42" s="1"/>
-      <c r="AG42" s="1"/>
-    </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="44" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
-      <c r="N44" s="1"/>
-      <c r="O44" s="1"/>
-      <c r="P44" s="1"/>
-      <c r="Q44" s="1"/>
-      <c r="R44" s="1"/>
-      <c r="S44" s="1"/>
-      <c r="T44" s="1"/>
-      <c r="U44" s="1"/>
-      <c r="V44" s="1"/>
-      <c r="W44" s="1"/>
-      <c r="X44" s="1"/>
-      <c r="Y44" s="1"/>
-      <c r="Z44" s="1"/>
-      <c r="AA44" s="1"/>
-      <c r="AB44" s="1"/>
-      <c r="AC44" s="1"/>
-      <c r="AD44" s="1"/>
-      <c r="AE44" s="1"/>
-      <c r="AF44" s="1"/>
-      <c r="AG44" s="1"/>
-    </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
-      <c r="L46" s="1"/>
-      <c r="M46" s="1"/>
-      <c r="N46" s="1"/>
-      <c r="O46" s="1"/>
-      <c r="P46" s="1"/>
-      <c r="Q46" s="1"/>
-      <c r="R46" s="1"/>
-      <c r="S46" s="1"/>
-      <c r="T46" s="1"/>
-      <c r="U46" s="1"/>
-      <c r="V46" s="1"/>
-      <c r="W46" s="1"/>
-      <c r="X46" s="1"/>
-      <c r="Y46" s="1"/>
-      <c r="Z46" s="1"/>
-      <c r="AA46" s="1"/>
-      <c r="AB46" s="1"/>
-      <c r="AC46" s="1"/>
-      <c r="AD46" s="1"/>
-      <c r="AE46" s="1"/>
-      <c r="AF46" s="1"/>
-      <c r="AG46" s="1"/>
-    </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
-      <c r="L48" s="1"/>
-      <c r="M48" s="1"/>
-      <c r="N48" s="1"/>
-      <c r="O48" s="1"/>
-      <c r="P48" s="1"/>
-      <c r="Q48" s="1"/>
-      <c r="R48" s="1"/>
-      <c r="S48" s="1"/>
-      <c r="T48" s="1"/>
-      <c r="U48" s="1"/>
-      <c r="V48" s="1"/>
-      <c r="W48" s="1"/>
-      <c r="X48" s="1"/>
-      <c r="Y48" s="1"/>
-      <c r="Z48" s="1"/>
-      <c r="AA48" s="1"/>
-      <c r="AB48" s="1"/>
-      <c r="AC48" s="1"/>
-      <c r="AD48" s="1"/>
-      <c r="AE48" s="1"/>
-      <c r="AF48" s="1"/>
-      <c r="AG48" s="1"/>
-    </row>
-    <row r="49" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="50" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B50" s="1"/>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
-      <c r="K50" s="1"/>
-      <c r="L50" s="1"/>
-      <c r="M50" s="1"/>
-      <c r="N50" s="1"/>
-      <c r="O50" s="1"/>
-      <c r="P50" s="1"/>
-      <c r="Q50" s="1"/>
-      <c r="R50" s="1"/>
-      <c r="S50" s="1"/>
-      <c r="T50" s="1"/>
-      <c r="U50" s="1"/>
-      <c r="V50" s="1"/>
-      <c r="W50" s="1"/>
-      <c r="X50" s="1"/>
-      <c r="Y50" s="1"/>
-      <c r="Z50" s="1"/>
-      <c r="AA50" s="1"/>
-      <c r="AB50" s="1"/>
-      <c r="AC50" s="1"/>
-      <c r="AD50" s="1"/>
-      <c r="AE50" s="1"/>
-      <c r="AF50" s="1"/>
-      <c r="AG50" s="1"/>
-    </row>
-    <row r="51" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="52" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
-      <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="1"/>
-      <c r="I52" s="1"/>
-      <c r="J52" s="1"/>
-      <c r="K52" s="1"/>
-      <c r="L52" s="1"/>
-      <c r="M52" s="1"/>
-      <c r="N52" s="1"/>
-      <c r="O52" s="1"/>
-      <c r="P52" s="1"/>
-      <c r="Q52" s="1"/>
-      <c r="R52" s="1"/>
-      <c r="S52" s="1"/>
-      <c r="T52" s="1"/>
-      <c r="U52" s="1"/>
-      <c r="V52" s="1"/>
-      <c r="W52" s="1"/>
-      <c r="X52" s="1"/>
-      <c r="Y52" s="1"/>
-      <c r="Z52" s="1"/>
-      <c r="AA52" s="1"/>
-      <c r="AB52" s="1"/>
-      <c r="AC52" s="1"/>
-      <c r="AD52" s="1"/>
-      <c r="AE52" s="1"/>
-      <c r="AF52" s="1"/>
-      <c r="AG52" s="1"/>
-    </row>
-    <row r="53" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="54" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B54" s="1"/>
-      <c r="C54" s="1"/>
-      <c r="D54" s="1"/>
-      <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
-      <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
-      <c r="L54" s="1"/>
-      <c r="M54" s="1"/>
-      <c r="N54" s="1"/>
-      <c r="O54" s="1"/>
-      <c r="P54" s="1"/>
-      <c r="Q54" s="1"/>
-      <c r="R54" s="1"/>
-      <c r="S54" s="1"/>
-      <c r="T54" s="1"/>
-      <c r="U54" s="1"/>
-      <c r="V54" s="1"/>
-      <c r="W54" s="1"/>
-      <c r="X54" s="1"/>
-      <c r="Y54" s="1"/>
-      <c r="Z54" s="1"/>
-      <c r="AA54" s="1"/>
-      <c r="AB54" s="1"/>
-      <c r="AC54" s="1"/>
-      <c r="AD54" s="1"/>
-      <c r="AE54" s="1"/>
-      <c r="AF54" s="1"/>
-      <c r="AG54" s="1"/>
-    </row>
-    <row r="55" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="56" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B56" s="1"/>
-      <c r="C56" s="1"/>
-      <c r="D56" s="1"/>
-      <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="1"/>
-      <c r="I56" s="1"/>
-      <c r="J56" s="1"/>
-      <c r="K56" s="1"/>
-      <c r="L56" s="1"/>
-      <c r="M56" s="1"/>
-      <c r="N56" s="1"/>
-      <c r="O56" s="1"/>
-      <c r="P56" s="1"/>
-      <c r="Q56" s="1"/>
-      <c r="R56" s="1"/>
-      <c r="S56" s="1"/>
-      <c r="T56" s="1"/>
-      <c r="U56" s="1"/>
-      <c r="V56" s="1"/>
-      <c r="W56" s="1"/>
-      <c r="X56" s="1"/>
-      <c r="Y56" s="1"/>
-      <c r="Z56" s="1"/>
-      <c r="AA56" s="1"/>
-      <c r="AB56" s="1"/>
-      <c r="AC56" s="1"/>
-      <c r="AD56" s="1"/>
-      <c r="AE56" s="1"/>
-      <c r="AF56" s="1"/>
-      <c r="AG56" s="1"/>
-    </row>
-  </sheetData>
+  <autoFilter ref="A3:AG3" xr:uid="{00000000-0001-0000-0800-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>